--- a/research/traditional_assets/database/data/zambia/zambia_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/zambia/zambia_oilfield_svcs_equip.xlsx
@@ -1265,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1402,22 +1402,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.176493998100249</v>
+        <v>0.1759055191068982</v>
       </c>
       <c r="C2">
-        <v>103.7</v>
+        <v>103.1320444496851</v>
       </c>
       <c r="D2">
-        <v>103.7</v>
+        <v>104.1690444496851</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1.037</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.037</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1438,28 +1438,28 @@
         <v>9.06</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0521611</v>
       </c>
       <c r="N2">
-        <v>9.06</v>
+        <v>9.007838900000001</v>
       </c>
       <c r="O2">
-        <v>3.171</v>
+        <v>3.152743615</v>
       </c>
       <c r="P2">
-        <v>5.889000000000001</v>
+        <v>5.855095285000001</v>
       </c>
       <c r="Q2">
-        <v>-3.170999999999999</v>
+        <v>-3.204904715</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.176493998100249</v>
+        <v>0.1773520900069679</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8045562062573437</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>173.6926560214413</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1484,22 +1484,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1759055191068982</v>
+        <v>0.1753170401135473</v>
       </c>
       <c r="C3">
-        <v>103.1320444496851</v>
+        <v>102.5683512389873</v>
       </c>
       <c r="D3">
-        <v>104.1690444496851</v>
+        <v>104.6423512389873</v>
       </c>
       <c r="E3">
-        <v>1.037</v>
+        <v>2.074</v>
       </c>
       <c r="F3">
-        <v>1.037</v>
+        <v>2.074</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1520,28 +1520,28 @@
         <v>9.06</v>
       </c>
       <c r="M3">
-        <v>0.0521611</v>
+        <v>0.1043222</v>
       </c>
       <c r="N3">
-        <v>9.007838900000001</v>
+        <v>8.9556778</v>
       </c>
       <c r="O3">
-        <v>3.152743615</v>
+        <v>3.13448723</v>
       </c>
       <c r="P3">
-        <v>5.855095285000001</v>
+        <v>5.821190570000001</v>
       </c>
       <c r="Q3">
-        <v>-3.204904715</v>
+        <v>-3.23880943</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1773520900069679</v>
+        <v>0.1782276939934156</v>
       </c>
       <c r="T3">
-        <v>0.8045562062573437</v>
+        <v>0.8099112912391399</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>173.6926560214413</v>
+        <v>86.84632801072063</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1566,22 +1566,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1753170401135473</v>
+        <v>0.1747285611201964</v>
       </c>
       <c r="C4">
-        <v>102.5683512389873</v>
+        <v>102.0089787327245</v>
       </c>
       <c r="D4">
-        <v>104.6423512389873</v>
+        <v>105.1199787327245</v>
       </c>
       <c r="E4">
-        <v>2.074</v>
+        <v>3.111</v>
       </c>
       <c r="F4">
-        <v>2.074</v>
+        <v>3.111</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1602,28 +1602,28 @@
         <v>9.06</v>
       </c>
       <c r="M4">
-        <v>0.1043222</v>
+        <v>0.1564833</v>
       </c>
       <c r="N4">
-        <v>8.9556778</v>
+        <v>8.903516700000001</v>
       </c>
       <c r="O4">
-        <v>3.13448723</v>
+        <v>3.116230845</v>
       </c>
       <c r="P4">
-        <v>5.821190570000001</v>
+        <v>5.787285855</v>
       </c>
       <c r="Q4">
-        <v>-3.23880943</v>
+        <v>-3.272714145</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1782276939934156</v>
+        <v>0.1791213516703056</v>
       </c>
       <c r="T4">
-        <v>0.8099112912391399</v>
+        <v>0.815376790344272</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>86.84632801072063</v>
+        <v>57.8975520071471</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1648,22 +1648,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1747285611201964</v>
+        <v>0.1741400821268456</v>
       </c>
       <c r="C5">
-        <v>102.0089787327245</v>
+        <v>101.4539863661976</v>
       </c>
       <c r="D5">
-        <v>105.1199787327245</v>
+        <v>105.6019863661976</v>
       </c>
       <c r="E5">
-        <v>3.111</v>
+        <v>4.148000000000001</v>
       </c>
       <c r="F5">
-        <v>3.111</v>
+        <v>4.148000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1684,28 +1684,28 @@
         <v>9.06</v>
       </c>
       <c r="M5">
-        <v>0.1564833</v>
+        <v>0.2086444</v>
       </c>
       <c r="N5">
-        <v>8.903516700000001</v>
+        <v>8.8513556</v>
       </c>
       <c r="O5">
-        <v>3.116230845</v>
+        <v>3.09797446</v>
       </c>
       <c r="P5">
-        <v>5.787285855</v>
+        <v>5.75338114</v>
       </c>
       <c r="Q5">
-        <v>-3.272714145</v>
+        <v>-3.30661886</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1791213516703056</v>
+        <v>0.1800336272154641</v>
       </c>
       <c r="T5">
-        <v>0.815376790344272</v>
+        <v>0.8209561540140946</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.8975520071471</v>
+        <v>43.42316400536031</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1730,22 +1730,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1741400821268456</v>
+        <v>0.1735516031334947</v>
       </c>
       <c r="C6">
-        <v>101.4539863661976</v>
+        <v>100.9034346698459</v>
       </c>
       <c r="D6">
-        <v>105.6019863661976</v>
+        <v>106.0884346698459</v>
       </c>
       <c r="E6">
-        <v>4.148000000000001</v>
+        <v>5.185</v>
       </c>
       <c r="F6">
-        <v>4.148000000000001</v>
+        <v>5.185</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1766,28 +1766,28 @@
         <v>9.06</v>
       </c>
       <c r="M6">
-        <v>0.2086444</v>
+        <v>0.2608055</v>
       </c>
       <c r="N6">
-        <v>8.8513556</v>
+        <v>8.7991945</v>
       </c>
       <c r="O6">
-        <v>3.09797446</v>
+        <v>3.079718075</v>
       </c>
       <c r="P6">
-        <v>5.75338114</v>
+        <v>5.719476425</v>
       </c>
       <c r="Q6">
-        <v>-3.30661886</v>
+        <v>-3.340523575000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1800336272154641</v>
+        <v>0.1809651085615734</v>
       </c>
       <c r="T6">
-        <v>0.8209561540140946</v>
+        <v>0.8266529779717028</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.42316400536031</v>
+        <v>34.73853120428825</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1812,22 +1812,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1735516031334947</v>
+        <v>0.1729631241401438</v>
       </c>
       <c r="C7">
-        <v>100.9034346698459</v>
+        <v>100.3573852945873</v>
       </c>
       <c r="D7">
-        <v>106.0884346698459</v>
+        <v>106.5793852945873</v>
       </c>
       <c r="E7">
-        <v>5.185</v>
+        <v>6.222</v>
       </c>
       <c r="F7">
-        <v>5.185</v>
+        <v>6.222</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>9.06</v>
       </c>
       <c r="M7">
-        <v>0.2608055</v>
+        <v>0.3129666</v>
       </c>
       <c r="N7">
-        <v>8.7991945</v>
+        <v>8.747033400000001</v>
       </c>
       <c r="O7">
-        <v>3.079718075</v>
+        <v>3.06146169</v>
       </c>
       <c r="P7">
-        <v>5.719476425</v>
+        <v>5.685571710000001</v>
       </c>
       <c r="Q7">
-        <v>-3.340523575000001</v>
+        <v>-3.374428289999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1809651085615734</v>
+        <v>0.1819164086597275</v>
       </c>
       <c r="T7">
-        <v>0.8266529779717028</v>
+        <v>0.8324710109496857</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.73853120428825</v>
+        <v>28.94877600357355</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1894,22 +1894,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1729631241401438</v>
+        <v>0.172374645146793</v>
       </c>
       <c r="C8">
-        <v>100.3573852945873</v>
+        <v>99.81590103786571</v>
       </c>
       <c r="D8">
-        <v>106.5793852945873</v>
+        <v>107.0749010378657</v>
       </c>
       <c r="E8">
-        <v>6.222</v>
+        <v>7.258999999999999</v>
       </c>
       <c r="F8">
-        <v>6.222</v>
+        <v>7.258999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1930,28 +1930,28 @@
         <v>9.06</v>
       </c>
       <c r="M8">
-        <v>0.3129666</v>
+        <v>0.3651276999999999</v>
       </c>
       <c r="N8">
-        <v>8.747033400000001</v>
+        <v>8.6948723</v>
       </c>
       <c r="O8">
-        <v>3.06146169</v>
+        <v>3.043205305</v>
       </c>
       <c r="P8">
-        <v>5.685571710000001</v>
+        <v>5.651666995</v>
       </c>
       <c r="Q8">
-        <v>-3.374428289999999</v>
+        <v>-3.408333005</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1819164086597275</v>
+        <v>0.1828881668245085</v>
       </c>
       <c r="T8">
-        <v>0.8324710109496857</v>
+        <v>0.8384141629164422</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.94877600357355</v>
+        <v>24.81323657449162</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1976,22 +1976,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1723746451467929</v>
+        <v>0.1717861661534421</v>
       </c>
       <c r="C9">
-        <v>99.81590103786574</v>
+        <v>99.27904587042744</v>
       </c>
       <c r="D9">
-        <v>107.0749010378657</v>
+        <v>107.5750458704274</v>
       </c>
       <c r="E9">
-        <v>7.259000000000001</v>
+        <v>8.296000000000001</v>
       </c>
       <c r="F9">
-        <v>7.259000000000001</v>
+        <v>8.296000000000001</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2012,28 +2012,28 @@
         <v>9.06</v>
       </c>
       <c r="M9">
-        <v>0.3651277000000001</v>
+        <v>0.4172888</v>
       </c>
       <c r="N9">
-        <v>8.6948723</v>
+        <v>8.642711200000001</v>
       </c>
       <c r="O9">
-        <v>3.043205305</v>
+        <v>3.02494892</v>
       </c>
       <c r="P9">
-        <v>5.651666995</v>
+        <v>5.617762280000001</v>
       </c>
       <c r="Q9">
-        <v>-3.408333005</v>
+        <v>-3.44223772</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1828881668245085</v>
+        <v>0.1838810501667849</v>
       </c>
       <c r="T9">
-        <v>0.8384141629164422</v>
+        <v>0.844486513838998</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.8132365744916</v>
+        <v>21.71158200268016</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2058,22 +2058,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1717861661534421</v>
+        <v>0.1711976871600912</v>
       </c>
       <c r="C10">
-        <v>99.27904587042744</v>
+        <v>98.74688496385255</v>
       </c>
       <c r="D10">
-        <v>107.5750458704274</v>
+        <v>108.0798849638525</v>
       </c>
       <c r="E10">
-        <v>8.296000000000001</v>
+        <v>9.333</v>
       </c>
       <c r="F10">
-        <v>8.296000000000001</v>
+        <v>9.333</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2094,28 +2094,28 @@
         <v>9.06</v>
       </c>
       <c r="M10">
-        <v>0.4172888</v>
+        <v>0.4694499</v>
       </c>
       <c r="N10">
-        <v>8.642711200000001</v>
+        <v>8.5905501</v>
       </c>
       <c r="O10">
-        <v>3.02494892</v>
+        <v>3.006692535</v>
       </c>
       <c r="P10">
-        <v>5.617762280000001</v>
+        <v>5.583857565000001</v>
       </c>
       <c r="Q10">
-        <v>-3.44223772</v>
+        <v>-3.476142435</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1838810501667849</v>
+        <v>0.1848957551209794</v>
       </c>
       <c r="T10">
-        <v>0.844486513838998</v>
+        <v>0.850692323023588</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.71158200268016</v>
+        <v>19.29918400238236</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2140,22 +2140,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1711976871600912</v>
+        <v>0.1706092081667403</v>
       </c>
       <c r="C11">
-        <v>98.74688496385255</v>
+        <v>98.21948471886449</v>
       </c>
       <c r="D11">
-        <v>108.0798849638525</v>
+        <v>108.5894847188645</v>
       </c>
       <c r="E11">
-        <v>9.333</v>
+        <v>10.37</v>
       </c>
       <c r="F11">
-        <v>9.333</v>
+        <v>10.37</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2176,28 +2176,28 @@
         <v>9.06</v>
       </c>
       <c r="M11">
-        <v>0.4694499</v>
+        <v>0.5216109999999999</v>
       </c>
       <c r="N11">
-        <v>8.5905501</v>
+        <v>8.538389</v>
       </c>
       <c r="O11">
-        <v>3.006692535</v>
+        <v>2.98843615</v>
       </c>
       <c r="P11">
-        <v>5.583857565000001</v>
+        <v>5.54995285</v>
       </c>
       <c r="Q11">
-        <v>-3.476142435</v>
+        <v>-3.51004715</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1848957551209794</v>
+        <v>0.1859330090741559</v>
       </c>
       <c r="T11">
-        <v>0.850692323023588</v>
+        <v>0.8570360390789465</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.29918400238236</v>
+        <v>17.36926560214413</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2222,22 +2222,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1706092081667403</v>
+        <v>0.1700207291733895</v>
       </c>
       <c r="C12">
-        <v>98.21948471886449</v>
+        <v>97.69691279444476</v>
       </c>
       <c r="D12">
-        <v>108.5894847188645</v>
+        <v>109.1039127944448</v>
       </c>
       <c r="E12">
-        <v>10.37</v>
+        <v>11.407</v>
       </c>
       <c r="F12">
-        <v>10.37</v>
+        <v>11.407</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2258,28 +2258,28 @@
         <v>9.06</v>
       </c>
       <c r="M12">
-        <v>0.521611</v>
+        <v>0.5737721</v>
       </c>
       <c r="N12">
-        <v>8.538389</v>
+        <v>8.486227900000001</v>
       </c>
       <c r="O12">
-        <v>2.98843615</v>
+        <v>2.970179765</v>
       </c>
       <c r="P12">
-        <v>5.54995285</v>
+        <v>5.516048135000001</v>
       </c>
       <c r="Q12">
-        <v>-3.51004715</v>
+        <v>-3.543951864999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1859330090741559</v>
+        <v>0.186993572104932</v>
       </c>
       <c r="T12">
-        <v>0.8570360390789465</v>
+        <v>0.8635223105512796</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.36926560214413</v>
+        <v>15.79024145649466</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2304,22 +2304,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1700207291733895</v>
+        <v>0.1694322501800386</v>
       </c>
       <c r="C13">
-        <v>97.69691279444476</v>
+        <v>97.17923813777887</v>
       </c>
       <c r="D13">
-        <v>109.1039127944448</v>
+        <v>109.6232381377789</v>
       </c>
       <c r="E13">
-        <v>11.407</v>
+        <v>12.444</v>
       </c>
       <c r="F13">
-        <v>11.407</v>
+        <v>12.444</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2340,28 +2340,28 @@
         <v>9.06</v>
       </c>
       <c r="M13">
-        <v>0.5737721</v>
+        <v>0.6259332</v>
       </c>
       <c r="N13">
-        <v>8.486227900000001</v>
+        <v>8.4340668</v>
       </c>
       <c r="O13">
-        <v>2.970179765</v>
+        <v>2.95192338</v>
       </c>
       <c r="P13">
-        <v>5.516048135000001</v>
+        <v>5.48214342</v>
       </c>
       <c r="Q13">
-        <v>-3.543951864999999</v>
+        <v>-3.577856580000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.186993572104932</v>
+        <v>0.188078238840953</v>
       </c>
       <c r="T13">
-        <v>0.8635223105512796</v>
+        <v>0.8701559972843473</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.79024145649466</v>
+        <v>14.47438800178677</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2386,22 +2386,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1694322501800386</v>
+        <v>0.1688437711866878</v>
       </c>
       <c r="C14">
-        <v>97.17923813777887</v>
+        <v>96.66653101506157</v>
       </c>
       <c r="D14">
-        <v>109.6232381377789</v>
+        <v>110.1475310150616</v>
       </c>
       <c r="E14">
-        <v>12.444</v>
+        <v>13.481</v>
       </c>
       <c r="F14">
-        <v>12.444</v>
+        <v>13.481</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2422,28 +2422,28 @@
         <v>9.06</v>
       </c>
       <c r="M14">
-        <v>0.6259332</v>
+        <v>0.6780943</v>
       </c>
       <c r="N14">
-        <v>8.4340668</v>
+        <v>8.381905700000001</v>
       </c>
       <c r="O14">
-        <v>2.95192338</v>
+        <v>2.933666995</v>
       </c>
       <c r="P14">
-        <v>5.48214342</v>
+        <v>5.448238705000001</v>
       </c>
       <c r="Q14">
-        <v>-3.577856580000001</v>
+        <v>-3.611761295</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.188078238840953</v>
+        <v>0.1891878404444687</v>
       </c>
       <c r="T14">
-        <v>0.8701559972843473</v>
+        <v>0.8769421825630028</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.47438800178677</v>
+        <v>13.36097354011087</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2468,22 +2468,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1688437711866878</v>
+        <v>0.1683917921933369</v>
       </c>
       <c r="C15">
-        <v>96.66653101506157</v>
+        <v>96.03562973747651</v>
       </c>
       <c r="D15">
-        <v>110.1475310150616</v>
+        <v>110.5536297374765</v>
       </c>
       <c r="E15">
-        <v>13.481</v>
+        <v>14.518</v>
       </c>
       <c r="F15">
-        <v>13.481</v>
+        <v>14.518</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2504,45 +2504,45 @@
         <v>9.06</v>
       </c>
       <c r="M15">
-        <v>0.6780943</v>
+        <v>0.7520324000000002</v>
       </c>
       <c r="N15">
-        <v>8.381905700000001</v>
+        <v>8.3079676</v>
       </c>
       <c r="O15">
-        <v>2.933666995</v>
+        <v>2.90778866</v>
       </c>
       <c r="P15">
-        <v>5.448238705000001</v>
+        <v>5.40017894</v>
       </c>
       <c r="Q15">
-        <v>-3.611761295</v>
+        <v>-3.659821060000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1891878404444687</v>
+        <v>0.1903232467364382</v>
       </c>
       <c r="T15">
-        <v>0.8769421825630028</v>
+        <v>0.8838861861039529</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.36097354011087</v>
+        <v>12.04735327892787</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2550,22 +2550,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1683917921933369</v>
+        <v>0.167813063199986</v>
       </c>
       <c r="C16">
-        <v>96.03562973747651</v>
+        <v>95.52300466235145</v>
       </c>
       <c r="D16">
-        <v>110.5536297374765</v>
+        <v>111.0780046623515</v>
       </c>
       <c r="E16">
-        <v>14.518</v>
+        <v>15.555</v>
       </c>
       <c r="F16">
-        <v>14.518</v>
+        <v>15.555</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2586,28 +2586,28 @@
         <v>9.06</v>
       </c>
       <c r="M16">
-        <v>0.7520324000000002</v>
+        <v>0.8057490000000002</v>
       </c>
       <c r="N16">
-        <v>8.3079676</v>
+        <v>8.254251</v>
       </c>
       <c r="O16">
-        <v>2.90778866</v>
+        <v>2.88898785</v>
       </c>
       <c r="P16">
-        <v>5.40017894</v>
+        <v>5.365263150000001</v>
       </c>
       <c r="Q16">
-        <v>-3.659821060000001</v>
+        <v>-3.69473685</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1903232467364382</v>
+        <v>0.1914853684705717</v>
       </c>
       <c r="T16">
-        <v>0.8838861861039529</v>
+        <v>0.8909935779635132</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.04735327892787</v>
+        <v>11.24419639366602</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2632,22 +2632,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.167813063199986</v>
+        <v>0.1672343342066351</v>
       </c>
       <c r="C17">
-        <v>95.52300466235147</v>
+        <v>95.01537769545328</v>
       </c>
       <c r="D17">
-        <v>111.0780046623515</v>
+        <v>111.6073776954533</v>
       </c>
       <c r="E17">
-        <v>15.555</v>
+        <v>16.592</v>
       </c>
       <c r="F17">
-        <v>15.555</v>
+        <v>16.592</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2668,28 +2668,28 @@
         <v>9.06</v>
       </c>
       <c r="M17">
-        <v>0.8057489999999999</v>
+        <v>0.8594656000000001</v>
       </c>
       <c r="N17">
-        <v>8.254251</v>
+        <v>8.2005344</v>
       </c>
       <c r="O17">
-        <v>2.88898785</v>
+        <v>2.87018704</v>
       </c>
       <c r="P17">
-        <v>5.365263150000001</v>
+        <v>5.330347360000001</v>
       </c>
       <c r="Q17">
-        <v>-3.69473685</v>
+        <v>-3.729652639999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1914853684705717</v>
+        <v>0.1926751597698037</v>
       </c>
       <c r="T17">
-        <v>0.8909935779635132</v>
+        <v>0.8982701934387775</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.24419639366602</v>
+        <v>10.54143411906189</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2714,22 +2714,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1672343342066351</v>
+        <v>0.1666556052132842</v>
       </c>
       <c r="C18">
-        <v>95.01537769545328</v>
+        <v>94.51282063858558</v>
       </c>
       <c r="D18">
-        <v>111.6073776954533</v>
+        <v>112.1418206385856</v>
       </c>
       <c r="E18">
-        <v>16.592</v>
+        <v>17.629</v>
       </c>
       <c r="F18">
-        <v>16.592</v>
+        <v>17.629</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2750,28 +2750,28 @@
         <v>9.06</v>
       </c>
       <c r="M18">
-        <v>0.8594656000000001</v>
+        <v>0.9131822000000001</v>
       </c>
       <c r="N18">
-        <v>8.2005344</v>
+        <v>8.146817800000001</v>
       </c>
       <c r="O18">
-        <v>2.87018704</v>
+        <v>2.85138623</v>
       </c>
       <c r="P18">
-        <v>5.330347360000001</v>
+        <v>5.295431570000001</v>
       </c>
       <c r="Q18">
-        <v>-3.729652639999999</v>
+        <v>-3.76456843</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1926751597698037</v>
+        <v>0.1938936207388967</v>
       </c>
       <c r="T18">
-        <v>0.8982701934387775</v>
+        <v>0.9057221490459758</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.54143411906189</v>
+        <v>9.921349759117074</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2796,22 +2796,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1666556052132842</v>
+        <v>0.1662757762199333</v>
       </c>
       <c r="C19">
-        <v>94.51282063858558</v>
+        <v>93.82937482335322</v>
       </c>
       <c r="D19">
-        <v>112.1418206385856</v>
+        <v>112.4953748233532</v>
       </c>
       <c r="E19">
-        <v>17.629</v>
+        <v>18.666</v>
       </c>
       <c r="F19">
-        <v>17.629</v>
+        <v>18.666</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2832,45 +2832,45 @@
         <v>9.06</v>
       </c>
       <c r="M19">
-        <v>0.9131822000000001</v>
+        <v>0.9986310000000002</v>
       </c>
       <c r="N19">
-        <v>8.146817800000001</v>
+        <v>8.061369000000001</v>
       </c>
       <c r="O19">
-        <v>2.85138623</v>
+        <v>2.82147915</v>
       </c>
       <c r="P19">
-        <v>5.295431570000001</v>
+        <v>5.239889850000001</v>
       </c>
       <c r="Q19">
-        <v>-3.76456843</v>
+        <v>-3.82011015</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1938936207388967</v>
+        <v>0.1951418002682114</v>
       </c>
       <c r="T19">
-        <v>0.9057221490459758</v>
+        <v>0.9133558596679838</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.921349759117074</v>
+        <v>9.072420143176007</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2878,22 +2878,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1662757762199334</v>
+        <v>0.1657080972265825</v>
       </c>
       <c r="C20">
-        <v>93.82937482335321</v>
+        <v>93.3249598831901</v>
       </c>
       <c r="D20">
-        <v>112.4953748233532</v>
+        <v>113.0279598831901</v>
       </c>
       <c r="E20">
-        <v>18.666</v>
+        <v>19.703</v>
       </c>
       <c r="F20">
-        <v>18.666</v>
+        <v>19.703</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2914,28 +2914,28 @@
         <v>9.06</v>
       </c>
       <c r="M20">
-        <v>0.998631</v>
+        <v>1.0541105</v>
       </c>
       <c r="N20">
-        <v>8.061369000000001</v>
+        <v>8.0058895</v>
       </c>
       <c r="O20">
-        <v>2.82147915</v>
+        <v>2.802061325</v>
       </c>
       <c r="P20">
-        <v>5.239889850000001</v>
+        <v>5.203828175</v>
       </c>
       <c r="Q20">
-        <v>-3.82011015</v>
+        <v>-3.856171825000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1951418002682114</v>
+        <v>0.1964207990451636</v>
       </c>
       <c r="T20">
-        <v>0.9133558596679838</v>
+        <v>0.9211780569720169</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.072420143176009</v>
+        <v>8.594924346166746</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2960,22 +2960,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1657080972265825</v>
+        <v>0.1651404182332316</v>
       </c>
       <c r="C21">
-        <v>93.3249598831901</v>
+        <v>92.8256117486427</v>
       </c>
       <c r="D21">
-        <v>113.0279598831901</v>
+        <v>113.5656117486427</v>
       </c>
       <c r="E21">
-        <v>19.703</v>
+        <v>20.74</v>
       </c>
       <c r="F21">
-        <v>19.703</v>
+        <v>20.74</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2996,28 +2996,28 @@
         <v>9.06</v>
       </c>
       <c r="M21">
-        <v>1.0541105</v>
+        <v>1.10959</v>
       </c>
       <c r="N21">
-        <v>8.0058895</v>
+        <v>7.950410000000001</v>
       </c>
       <c r="O21">
-        <v>2.802061325</v>
+        <v>2.7826435</v>
       </c>
       <c r="P21">
-        <v>5.203828175</v>
+        <v>5.167766500000001</v>
       </c>
       <c r="Q21">
-        <v>-3.856171825000001</v>
+        <v>-3.8922335</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1964207990451636</v>
+        <v>0.1977317727915396</v>
       </c>
       <c r="T21">
-        <v>0.9211780569720169</v>
+        <v>0.9291958092086507</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.594924346166746</v>
+        <v>8.165178128858408</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3042,22 +3042,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1651404182332316</v>
+        <v>0.1645727392398807</v>
       </c>
       <c r="C22">
-        <v>92.8256117486427</v>
+        <v>92.33140307070309</v>
       </c>
       <c r="D22">
-        <v>113.5656117486427</v>
+        <v>114.1084030707031</v>
       </c>
       <c r="E22">
-        <v>20.74</v>
+        <v>21.777</v>
       </c>
       <c r="F22">
-        <v>20.74</v>
+        <v>21.777</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3078,28 +3078,28 @@
         <v>9.06</v>
       </c>
       <c r="M22">
-        <v>1.10959</v>
+        <v>1.1650695</v>
       </c>
       <c r="N22">
-        <v>7.950410000000001</v>
+        <v>7.894930500000001</v>
       </c>
       <c r="O22">
-        <v>2.7826435</v>
+        <v>2.763225675</v>
       </c>
       <c r="P22">
-        <v>5.167766500000001</v>
+        <v>5.131704825000001</v>
       </c>
       <c r="Q22">
-        <v>-3.8922335</v>
+        <v>-3.928295175</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1977317727915396</v>
+        <v>0.1990759357466845</v>
       </c>
       <c r="T22">
-        <v>0.9291958092086507</v>
+        <v>0.9374165425145663</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.165178128858408</v>
+        <v>7.776360122722293</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3124,22 +3124,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1645727392398807</v>
+        <v>0.1641194602465299</v>
       </c>
       <c r="C23">
-        <v>92.33140307070309</v>
+        <v>91.73154960576161</v>
       </c>
       <c r="D23">
-        <v>114.1084030707031</v>
+        <v>114.5455496057616</v>
       </c>
       <c r="E23">
-        <v>21.777</v>
+        <v>22.814</v>
       </c>
       <c r="F23">
-        <v>21.777</v>
+        <v>22.814</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3160,45 +3160,45 @@
         <v>9.06</v>
       </c>
       <c r="M23">
-        <v>1.1650695</v>
+        <v>1.2388002</v>
       </c>
       <c r="N23">
-        <v>7.894930500000001</v>
+        <v>7.8211998</v>
       </c>
       <c r="O23">
-        <v>2.763225675</v>
+        <v>2.73741993</v>
       </c>
       <c r="P23">
-        <v>5.131704825000001</v>
+        <v>5.083779870000001</v>
       </c>
       <c r="Q23">
-        <v>-3.928295175</v>
+        <v>-3.97622013</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1990759357466845</v>
+        <v>0.2004545644186281</v>
       </c>
       <c r="T23">
-        <v>0.9374165425145663</v>
+        <v>0.9458480638539669</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.35</v>
       </c>
       <c r="W23">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.776360122722293</v>
+        <v>7.313528041083623</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3206,22 +3206,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1641194602465299</v>
+        <v>0.163556981253179</v>
       </c>
       <c r="C24">
-        <v>91.73154960576161</v>
+        <v>91.2416888475238</v>
       </c>
       <c r="D24">
-        <v>114.5455496057616</v>
+        <v>115.0926888475238</v>
       </c>
       <c r="E24">
-        <v>22.814</v>
+        <v>23.851</v>
       </c>
       <c r="F24">
-        <v>22.814</v>
+        <v>23.851</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3242,28 +3242,28 @@
         <v>9.06</v>
       </c>
       <c r="M24">
-        <v>1.2388002</v>
+        <v>1.2951093</v>
       </c>
       <c r="N24">
-        <v>7.8211998</v>
+        <v>7.7648907</v>
       </c>
       <c r="O24">
-        <v>2.73741993</v>
+        <v>2.717711745</v>
       </c>
       <c r="P24">
-        <v>5.083779870000001</v>
+        <v>5.047178955000001</v>
       </c>
       <c r="Q24">
-        <v>-3.97622013</v>
+        <v>-4.012821045</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2004545644186281</v>
+        <v>0.2018690016275052</v>
       </c>
       <c r="T24">
-        <v>0.9458480638539669</v>
+        <v>0.9544985857476378</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.313528041083623</v>
+        <v>6.995548561036508</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3288,22 +3288,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.163556981253179</v>
+        <v>0.1629945022598281</v>
       </c>
       <c r="C25">
-        <v>91.2416888475238</v>
+        <v>90.75708011602779</v>
       </c>
       <c r="D25">
-        <v>115.0926888475238</v>
+        <v>115.6450801160278</v>
       </c>
       <c r="E25">
-        <v>23.851</v>
+        <v>24.888</v>
       </c>
       <c r="F25">
-        <v>23.851</v>
+        <v>24.888</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3324,28 +3324,28 @@
         <v>9.06</v>
       </c>
       <c r="M25">
-        <v>1.2951093</v>
+        <v>1.3514184</v>
       </c>
       <c r="N25">
-        <v>7.7648907</v>
+        <v>7.7085816</v>
       </c>
       <c r="O25">
-        <v>2.717711745</v>
+        <v>2.69800356</v>
       </c>
       <c r="P25">
-        <v>5.047178955000001</v>
+        <v>5.01057804</v>
       </c>
       <c r="Q25">
-        <v>-4.012821045</v>
+        <v>-4.04942196</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2018690016275052</v>
+        <v>0.2033206608681949</v>
       </c>
       <c r="T25">
-        <v>0.9544985857476378</v>
+        <v>0.9633767529542999</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.995548561036508</v>
+        <v>6.704067370993321</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3370,22 +3370,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1629945022598281</v>
+        <v>0.1624320232664773</v>
       </c>
       <c r="C26">
-        <v>90.75708011602779</v>
+        <v>90.27779939781567</v>
       </c>
       <c r="D26">
-        <v>115.6450801160278</v>
+        <v>116.2027993978157</v>
       </c>
       <c r="E26">
-        <v>24.888</v>
+        <v>25.925</v>
       </c>
       <c r="F26">
-        <v>24.888</v>
+        <v>25.925</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3406,28 +3406,28 @@
         <v>9.06</v>
       </c>
       <c r="M26">
-        <v>1.3514184</v>
+        <v>1.4077275</v>
       </c>
       <c r="N26">
-        <v>7.7085816</v>
+        <v>7.6522725</v>
       </c>
       <c r="O26">
-        <v>2.69800356</v>
+        <v>2.678295375</v>
       </c>
       <c r="P26">
-        <v>5.01057804</v>
+        <v>4.973977125000001</v>
       </c>
       <c r="Q26">
-        <v>-4.04942196</v>
+        <v>-4.086022874999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2033206608681949</v>
+        <v>0.2048110310219697</v>
       </c>
       <c r="T26">
-        <v>0.9633767529542999</v>
+        <v>0.9724916712864732</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.704067370993321</v>
+        <v>6.435904676153588</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3452,22 +3452,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1624320232664773</v>
+        <v>0.1618695442731264</v>
       </c>
       <c r="C27">
-        <v>90.27779939781567</v>
+        <v>89.80392415236824</v>
       </c>
       <c r="D27">
-        <v>116.2027993978157</v>
+        <v>116.7659241523682</v>
       </c>
       <c r="E27">
-        <v>25.925</v>
+        <v>26.962</v>
       </c>
       <c r="F27">
-        <v>25.925</v>
+        <v>26.962</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3488,28 +3488,28 @@
         <v>9.06</v>
       </c>
       <c r="M27">
-        <v>1.4077275</v>
+        <v>1.4640366</v>
       </c>
       <c r="N27">
-        <v>7.6522725</v>
+        <v>7.5959634</v>
       </c>
       <c r="O27">
-        <v>2.678295375</v>
+        <v>2.65858719</v>
       </c>
       <c r="P27">
-        <v>4.973977125000001</v>
+        <v>4.93737621</v>
       </c>
       <c r="Q27">
-        <v>-4.086022874999999</v>
+        <v>-4.12262379</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2048110310219697</v>
+        <v>0.2063416814501708</v>
       </c>
       <c r="T27">
-        <v>0.9724916712864732</v>
+        <v>0.981852938762759</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.435904676153588</v>
+        <v>6.188369880916911</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3534,22 +3534,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1618695442731264</v>
+        <v>0.1614825652797755</v>
       </c>
       <c r="C28">
-        <v>89.80392415236824</v>
+        <v>89.1575271760554</v>
       </c>
       <c r="D28">
-        <v>116.7659241523682</v>
+        <v>117.1565271760554</v>
       </c>
       <c r="E28">
-        <v>26.962</v>
+        <v>27.999</v>
       </c>
       <c r="F28">
-        <v>26.962</v>
+        <v>27.999</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3570,45 +3570,45 @@
         <v>9.06</v>
       </c>
       <c r="M28">
-        <v>1.4640366</v>
+        <v>1.5483447</v>
       </c>
       <c r="N28">
-        <v>7.5959634</v>
+        <v>7.5116553</v>
       </c>
       <c r="O28">
-        <v>2.65858719</v>
+        <v>2.629079355</v>
       </c>
       <c r="P28">
-        <v>4.93737621</v>
+        <v>4.882575945</v>
       </c>
       <c r="Q28">
-        <v>-4.12262379</v>
+        <v>-4.177424055</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2063416814501708</v>
+        <v>0.2079142675065418</v>
       </c>
       <c r="T28">
-        <v>0.981852938762759</v>
+        <v>0.9914706793205871</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.35</v>
       </c>
       <c r="W28">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.188369880916911</v>
+        <v>5.851410218926056</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3616,22 +3616,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1614825652797755</v>
+        <v>0.1609265862864246</v>
       </c>
       <c r="C29">
-        <v>89.1575271760554</v>
+        <v>88.68630933068106</v>
       </c>
       <c r="D29">
-        <v>117.1565271760554</v>
+        <v>117.7223093306811</v>
       </c>
       <c r="E29">
-        <v>27.999</v>
+        <v>29.036</v>
       </c>
       <c r="F29">
-        <v>27.999</v>
+        <v>29.036</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3652,28 +3652,28 @@
         <v>9.06</v>
       </c>
       <c r="M29">
-        <v>1.5483447</v>
+        <v>1.6056908</v>
       </c>
       <c r="N29">
-        <v>7.5116553</v>
+        <v>7.4543092</v>
       </c>
       <c r="O29">
-        <v>2.629079355</v>
+        <v>2.60900822</v>
       </c>
       <c r="P29">
-        <v>4.882575945</v>
+        <v>4.84530098</v>
       </c>
       <c r="Q29">
-        <v>-4.177424055</v>
+        <v>-4.21469902</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2079142675065418</v>
+        <v>0.2095305365089231</v>
       </c>
       <c r="T29">
-        <v>0.9914706793205871</v>
+        <v>1.001355579338355</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.851410218926056</v>
+        <v>5.642431282535839</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3698,22 +3698,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1609265862864246</v>
+        <v>0.1603706072930738</v>
       </c>
       <c r="C30">
-        <v>88.68630933068106</v>
+        <v>88.22058264923116</v>
       </c>
       <c r="D30">
-        <v>117.7223093306811</v>
+        <v>118.2935826492312</v>
       </c>
       <c r="E30">
-        <v>29.036</v>
+        <v>30.073</v>
       </c>
       <c r="F30">
-        <v>29.036</v>
+        <v>30.073</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3734,28 +3734,28 @@
         <v>9.06</v>
       </c>
       <c r="M30">
-        <v>1.6056908</v>
+        <v>1.6630369</v>
       </c>
       <c r="N30">
-        <v>7.4543092</v>
+        <v>7.396963100000001</v>
       </c>
       <c r="O30">
-        <v>2.60900822</v>
+        <v>2.588937085</v>
       </c>
       <c r="P30">
-        <v>4.84530098</v>
+        <v>4.808026015000001</v>
       </c>
       <c r="Q30">
-        <v>-4.21469902</v>
+        <v>-4.251973984999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2095305365089231</v>
+        <v>0.2111923342155969</v>
       </c>
       <c r="T30">
-        <v>1.001355579338355</v>
+        <v>1.011518927243947</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.642431282535839</v>
+        <v>5.447864686586328</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3780,22 +3780,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1603706072930738</v>
+        <v>0.1598146282997229</v>
       </c>
       <c r="C31">
-        <v>88.22058264923118</v>
+        <v>87.76042746276063</v>
       </c>
       <c r="D31">
-        <v>118.2935826492312</v>
+        <v>118.8704274627606</v>
       </c>
       <c r="E31">
-        <v>30.073</v>
+        <v>31.11</v>
       </c>
       <c r="F31">
-        <v>30.073</v>
+        <v>31.11</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3816,28 +3816,28 @@
         <v>9.06</v>
       </c>
       <c r="M31">
-        <v>1.6630369</v>
+        <v>1.720383</v>
       </c>
       <c r="N31">
-        <v>7.396963100000001</v>
+        <v>7.339617000000001</v>
       </c>
       <c r="O31">
-        <v>2.588937085</v>
+        <v>2.56886595</v>
       </c>
       <c r="P31">
-        <v>4.808026015000001</v>
+        <v>4.77075105</v>
       </c>
       <c r="Q31">
-        <v>-4.251973984999999</v>
+        <v>-4.28924895</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2111923342155969</v>
+        <v>0.212901611856747</v>
       </c>
       <c r="T31">
-        <v>1.011518927243947</v>
+        <v>1.02197265651827</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.447864686586329</v>
+        <v>5.266269197033451</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3862,22 +3862,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1598146282997229</v>
+        <v>0.159258649306372</v>
       </c>
       <c r="C32">
-        <v>87.76042746276063</v>
+        <v>87.30592567690269</v>
       </c>
       <c r="D32">
-        <v>118.8704274627606</v>
+        <v>119.4529256769027</v>
       </c>
       <c r="E32">
-        <v>31.11</v>
+        <v>32.147</v>
       </c>
       <c r="F32">
-        <v>31.11</v>
+        <v>32.147</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3898,28 +3898,28 @@
         <v>9.06</v>
       </c>
       <c r="M32">
-        <v>1.720383</v>
+        <v>1.7777291</v>
       </c>
       <c r="N32">
-        <v>7.339617000000001</v>
+        <v>7.2822709</v>
       </c>
       <c r="O32">
-        <v>2.56886595</v>
+        <v>2.548794815</v>
       </c>
       <c r="P32">
-        <v>4.77075105</v>
+        <v>4.733476085</v>
       </c>
       <c r="Q32">
-        <v>-4.28924895</v>
+        <v>-4.326523915</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.212901611856747</v>
+        <v>0.2146604337773508</v>
       </c>
       <c r="T32">
-        <v>1.02197265651827</v>
+        <v>1.032729392438226</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3936,7 +3936,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.266269197033451</v>
+        <v>5.096389545516243</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3944,22 +3944,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.159258649306372</v>
+        <v>0.1587026703130211</v>
       </c>
       <c r="C33">
-        <v>87.30592567690269</v>
+        <v>86.85716081063811</v>
       </c>
       <c r="D33">
-        <v>119.4529256769027</v>
+        <v>120.0411608106381</v>
       </c>
       <c r="E33">
-        <v>32.147</v>
+        <v>33.184</v>
       </c>
       <c r="F33">
-        <v>32.147</v>
+        <v>33.184</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3980,28 +3980,28 @@
         <v>9.06</v>
       </c>
       <c r="M33">
-        <v>1.7777291</v>
+        <v>1.8350752</v>
       </c>
       <c r="N33">
-        <v>7.2822709</v>
+        <v>7.2249248</v>
       </c>
       <c r="O33">
-        <v>2.548794815</v>
+        <v>2.52872368</v>
       </c>
       <c r="P33">
-        <v>4.733476085</v>
+        <v>4.69620112</v>
       </c>
       <c r="Q33">
-        <v>-4.326523915</v>
+        <v>-4.36379888</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2146604337773508</v>
+        <v>0.2164709857544429</v>
       </c>
       <c r="T33">
-        <v>1.032729392438226</v>
+        <v>1.043802502944063</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.096389545516243</v>
+        <v>4.93712737221886</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4026,22 +4026,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1587026703130211</v>
+        <v>0.1581466913196703</v>
       </c>
       <c r="C34">
-        <v>86.85716081063811</v>
+        <v>86.41421803621553</v>
       </c>
       <c r="D34">
-        <v>120.0411608106381</v>
+        <v>120.6352180362155</v>
       </c>
       <c r="E34">
-        <v>33.184</v>
+        <v>34.221</v>
       </c>
       <c r="F34">
-        <v>33.184</v>
+        <v>34.221</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4062,28 +4062,28 @@
         <v>9.06</v>
       </c>
       <c r="M34">
-        <v>1.8350752</v>
+        <v>1.8924213</v>
       </c>
       <c r="N34">
-        <v>7.2249248</v>
+        <v>7.1675787</v>
       </c>
       <c r="O34">
-        <v>2.52872368</v>
+        <v>2.508652545</v>
       </c>
       <c r="P34">
-        <v>4.69620112</v>
+        <v>4.658926155</v>
       </c>
       <c r="Q34">
-        <v>-4.36379888</v>
+        <v>-4.401073845000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2164709857544429</v>
+        <v>0.2183355840592094</v>
       </c>
       <c r="T34">
-        <v>1.043802502944063</v>
+        <v>1.055206154062014</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.93712737221886</v>
+        <v>4.787517451848592</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4108,22 +4108,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1581466913196703</v>
+        <v>0.1575907123263194</v>
       </c>
       <c r="C35">
-        <v>86.41421803621553</v>
+        <v>85.97718422026358</v>
       </c>
       <c r="D35">
-        <v>120.6352180362155</v>
+        <v>121.2351842202636</v>
       </c>
       <c r="E35">
-        <v>34.221</v>
+        <v>35.258</v>
       </c>
       <c r="F35">
-        <v>34.221</v>
+        <v>35.258</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4144,28 +4144,28 @@
         <v>9.06</v>
       </c>
       <c r="M35">
-        <v>1.8924213</v>
+        <v>1.9497674</v>
       </c>
       <c r="N35">
-        <v>7.1675787</v>
+        <v>7.1102326</v>
       </c>
       <c r="O35">
-        <v>2.508652545</v>
+        <v>2.48858141</v>
       </c>
       <c r="P35">
-        <v>4.658926155</v>
+        <v>4.62165119</v>
       </c>
       <c r="Q35">
-        <v>-4.401073845000001</v>
+        <v>-4.438348810000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2183355840592094</v>
+        <v>0.2202566853429082</v>
       </c>
       <c r="T35">
-        <v>1.055206154062014</v>
+        <v>1.066955370365358</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.787517451848592</v>
+        <v>4.646708115029515</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4190,22 +4190,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1575907123263194</v>
+        <v>0.1570347333329685</v>
       </c>
       <c r="C36">
-        <v>85.97718422026358</v>
+        <v>85.54614796613535</v>
       </c>
       <c r="D36">
-        <v>121.2351842202636</v>
+        <v>121.8411479661354</v>
       </c>
       <c r="E36">
-        <v>35.258</v>
+        <v>36.295</v>
       </c>
       <c r="F36">
-        <v>35.258</v>
+        <v>36.295</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4226,28 +4226,28 @@
         <v>9.06</v>
       </c>
       <c r="M36">
-        <v>1.9497674</v>
+        <v>2.0071135</v>
       </c>
       <c r="N36">
-        <v>7.1102326</v>
+        <v>7.052886500000001</v>
       </c>
       <c r="O36">
-        <v>2.48858141</v>
+        <v>2.468510275</v>
       </c>
       <c r="P36">
-        <v>4.62165119</v>
+        <v>4.584376225000001</v>
       </c>
       <c r="Q36">
-        <v>-4.438348810000001</v>
+        <v>-4.475623775</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2202566853429082</v>
+        <v>0.2222368974353362</v>
       </c>
       <c r="T36">
-        <v>1.066955370365358</v>
+        <v>1.079066101016497</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.646708115029515</v>
+        <v>4.513945026028672</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4272,22 +4272,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1570347333329685</v>
+        <v>0.1570637543396177</v>
       </c>
       <c r="C37">
-        <v>85.54614796613535</v>
+        <v>84.47736805014877</v>
       </c>
       <c r="D37">
-        <v>121.8411479661354</v>
+        <v>121.8093680501488</v>
       </c>
       <c r="E37">
-        <v>36.295</v>
+        <v>37.33200000000001</v>
       </c>
       <c r="F37">
-        <v>36.295</v>
+        <v>37.33200000000001</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4308,45 +4308,45 @@
         <v>9.06</v>
       </c>
       <c r="M37">
-        <v>2.0071135</v>
+        <v>2.157789600000001</v>
       </c>
       <c r="N37">
-        <v>7.052886500000001</v>
+        <v>6.9022104</v>
       </c>
       <c r="O37">
-        <v>2.468510275</v>
+        <v>2.41577364</v>
       </c>
       <c r="P37">
-        <v>4.584376225000001</v>
+        <v>4.48643676</v>
       </c>
       <c r="Q37">
-        <v>-4.475623775</v>
+        <v>-4.57356324</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2222368974353362</v>
+        <v>0.2242789911556526</v>
       </c>
       <c r="T37">
-        <v>1.079066101016497</v>
+        <v>1.091555292000485</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.35</v>
       </c>
       <c r="W37">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.513945026028672</v>
+        <v>4.19874115622765</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4354,22 +4354,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1570637543396177</v>
+        <v>0.1565240253462668</v>
       </c>
       <c r="C38">
-        <v>84.47736805014878</v>
+        <v>84.03413302024278</v>
       </c>
       <c r="D38">
-        <v>121.8093680501488</v>
+        <v>122.4031330202428</v>
       </c>
       <c r="E38">
-        <v>37.332</v>
+        <v>38.369</v>
       </c>
       <c r="F38">
-        <v>37.332</v>
+        <v>38.369</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4390,28 +4390,28 @@
         <v>9.06</v>
       </c>
       <c r="M38">
-        <v>2.1577896</v>
+        <v>2.2177282</v>
       </c>
       <c r="N38">
-        <v>6.9022104</v>
+        <v>6.842271800000001</v>
       </c>
       <c r="O38">
-        <v>2.41577364</v>
+        <v>2.39479513</v>
       </c>
       <c r="P38">
-        <v>4.48643676</v>
+        <v>4.44747667</v>
       </c>
       <c r="Q38">
-        <v>-4.57356324</v>
+        <v>-4.61252333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2242789911556526</v>
+        <v>0.2263859132480426</v>
       </c>
       <c r="T38">
-        <v>1.091555292000485</v>
+        <v>1.104440965237932</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.198741156227651</v>
+        <v>4.085261665518795</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4436,22 +4436,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1565240253462668</v>
+        <v>0.1568487963529159</v>
       </c>
       <c r="C39">
-        <v>84.03413302024278</v>
+        <v>82.63915535606665</v>
       </c>
       <c r="D39">
-        <v>122.4031330202428</v>
+        <v>122.0451553560666</v>
       </c>
       <c r="E39">
-        <v>38.369</v>
+        <v>39.406</v>
       </c>
       <c r="F39">
-        <v>38.369</v>
+        <v>39.406</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4472,45 +4472,45 @@
         <v>9.06</v>
       </c>
       <c r="M39">
-        <v>2.2177282</v>
+        <v>2.4155878</v>
       </c>
       <c r="N39">
-        <v>6.842271800000001</v>
+        <v>6.644412200000001</v>
       </c>
       <c r="O39">
-        <v>2.39479513</v>
+        <v>2.32554427</v>
       </c>
       <c r="P39">
-        <v>4.44747667</v>
+        <v>4.318867930000001</v>
       </c>
       <c r="Q39">
-        <v>-4.61252333</v>
+        <v>-4.74113207</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2263859132480426</v>
+        <v>0.2285608005692192</v>
       </c>
       <c r="T39">
-        <v>1.104440965237932</v>
+        <v>1.117742305354006</v>
       </c>
       <c r="U39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.35</v>
       </c>
       <c r="W39">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.085261665518795</v>
+        <v>3.750639906361508</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4518,22 +4518,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1568487963529159</v>
+        <v>0.1563318173595651</v>
       </c>
       <c r="C40">
-        <v>82.63915535606665</v>
+        <v>82.17298448985417</v>
       </c>
       <c r="D40">
-        <v>122.0451553560666</v>
+        <v>122.6159844898542</v>
       </c>
       <c r="E40">
-        <v>39.406</v>
+        <v>40.443</v>
       </c>
       <c r="F40">
-        <v>39.406</v>
+        <v>40.443</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4554,28 +4554,28 @@
         <v>9.06</v>
       </c>
       <c r="M40">
-        <v>2.4155878</v>
+        <v>2.4791559</v>
       </c>
       <c r="N40">
-        <v>6.644412200000001</v>
+        <v>6.5808441</v>
       </c>
       <c r="O40">
-        <v>2.32554427</v>
+        <v>2.303295435</v>
       </c>
       <c r="P40">
-        <v>4.318867930000001</v>
+        <v>4.277548665</v>
       </c>
       <c r="Q40">
-        <v>-4.74113207</v>
+        <v>-4.782451335</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2285608005692192</v>
+        <v>0.2308069956714182</v>
       </c>
       <c r="T40">
-        <v>1.117742305354006</v>
+        <v>1.131479754982083</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.750639906361508</v>
+        <v>3.654469652352238</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4600,22 +4600,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1563318173595651</v>
+        <v>0.1558148383662142</v>
       </c>
       <c r="C41">
-        <v>82.17298448985417</v>
+        <v>81.71217847578981</v>
       </c>
       <c r="D41">
-        <v>122.6159844898542</v>
+        <v>123.1921784757898</v>
       </c>
       <c r="E41">
-        <v>40.443</v>
+        <v>41.48</v>
       </c>
       <c r="F41">
-        <v>40.443</v>
+        <v>41.48</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4636,28 +4636,28 @@
         <v>9.06</v>
       </c>
       <c r="M41">
-        <v>2.4791559</v>
+        <v>2.542724</v>
       </c>
       <c r="N41">
-        <v>6.5808441</v>
+        <v>6.517276000000001</v>
       </c>
       <c r="O41">
-        <v>2.303295435</v>
+        <v>2.2810466</v>
       </c>
       <c r="P41">
-        <v>4.277548665</v>
+        <v>4.236229400000001</v>
       </c>
       <c r="Q41">
-        <v>-4.782451335</v>
+        <v>-4.8237706</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2308069956714182</v>
+        <v>0.2331280639436903</v>
       </c>
       <c r="T41">
-        <v>1.131479754982083</v>
+        <v>1.145675119597763</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.654469652352238</v>
+        <v>3.563107911043432</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4682,22 +4682,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1558148383662142</v>
+        <v>0.1560440593728633</v>
       </c>
       <c r="C42">
-        <v>81.71217847578981</v>
+        <v>80.41903555686832</v>
       </c>
       <c r="D42">
-        <v>123.1921784757898</v>
+        <v>122.9360355568683</v>
       </c>
       <c r="E42">
-        <v>41.48</v>
+        <v>42.517</v>
       </c>
       <c r="F42">
-        <v>41.48</v>
+        <v>42.517</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4718,45 +4718,45 @@
         <v>9.06</v>
       </c>
       <c r="M42">
-        <v>2.542724</v>
+        <v>2.725339700000001</v>
       </c>
       <c r="N42">
-        <v>6.517276000000001</v>
+        <v>6.334660299999999</v>
       </c>
       <c r="O42">
-        <v>2.2810466</v>
+        <v>2.217131105</v>
       </c>
       <c r="P42">
-        <v>4.236229400000001</v>
+        <v>4.117529194999999</v>
       </c>
       <c r="Q42">
-        <v>-4.8237706</v>
+        <v>-4.942470805000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2331280639436903</v>
+        <v>0.2355278124963785</v>
       </c>
       <c r="T42">
-        <v>1.145675119597763</v>
+        <v>1.160351683013974</v>
       </c>
       <c r="U42">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.35</v>
       </c>
       <c r="W42">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.563107911043432</v>
+        <v>3.324356226124765</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4764,22 +4764,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1560440593728633</v>
+        <v>0.1555452803795124</v>
       </c>
       <c r="C43">
-        <v>80.41903555686832</v>
+        <v>79.94076493319828</v>
       </c>
       <c r="D43">
-        <v>122.9360355568683</v>
+        <v>123.4947649331983</v>
       </c>
       <c r="E43">
-        <v>42.517</v>
+        <v>43.554</v>
       </c>
       <c r="F43">
-        <v>42.517</v>
+        <v>43.554</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4800,28 +4800,28 @@
         <v>9.06</v>
       </c>
       <c r="M43">
-        <v>2.725339700000001</v>
+        <v>2.7918114</v>
       </c>
       <c r="N43">
-        <v>6.334660299999999</v>
+        <v>6.2681886</v>
       </c>
       <c r="O43">
-        <v>2.217131105</v>
+        <v>2.19386601</v>
       </c>
       <c r="P43">
-        <v>4.117529194999999</v>
+        <v>4.07432259</v>
       </c>
       <c r="Q43">
-        <v>-4.942470805000001</v>
+        <v>-4.98567741</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2355278124963785</v>
+        <v>0.2380103109991594</v>
       </c>
       <c r="T43">
-        <v>1.160351683013974</v>
+        <v>1.175534334823847</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.324356226124765</v>
+        <v>3.245204887407509</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4846,22 +4846,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1555452803795125</v>
+        <v>0.1550465013861616</v>
       </c>
       <c r="C44">
-        <v>79.94076493319825</v>
+        <v>79.46759621160004</v>
       </c>
       <c r="D44">
-        <v>123.4947649331983</v>
+        <v>124.0585962116</v>
       </c>
       <c r="E44">
-        <v>43.554</v>
+        <v>44.591</v>
       </c>
       <c r="F44">
-        <v>43.554</v>
+        <v>44.591</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4882,28 +4882,28 @@
         <v>9.06</v>
       </c>
       <c r="M44">
-        <v>2.7918114</v>
+        <v>2.8582831</v>
       </c>
       <c r="N44">
-        <v>6.2681886</v>
+        <v>6.2017169</v>
       </c>
       <c r="O44">
-        <v>2.19386601</v>
+        <v>2.170600915</v>
       </c>
       <c r="P44">
-        <v>4.07432259</v>
+        <v>4.031115985</v>
       </c>
       <c r="Q44">
-        <v>-4.98567741</v>
+        <v>-5.028884015000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2380103109991594</v>
+        <v>0.2405799147125642</v>
       </c>
       <c r="T44">
-        <v>1.175534334823847</v>
+        <v>1.191249711258629</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.245204887407509</v>
+        <v>3.169735006305009</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4928,22 +4928,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1550465013861616</v>
+        <v>0.1545477223928107</v>
       </c>
       <c r="C45">
-        <v>79.46759621160004</v>
+        <v>78.99959959275992</v>
       </c>
       <c r="D45">
-        <v>124.0585962116</v>
+        <v>124.6275995927599</v>
       </c>
       <c r="E45">
-        <v>44.591</v>
+        <v>45.628</v>
       </c>
       <c r="F45">
-        <v>44.591</v>
+        <v>45.628</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4964,28 +4964,28 @@
         <v>9.06</v>
       </c>
       <c r="M45">
-        <v>2.8582831</v>
+        <v>2.9247548</v>
       </c>
       <c r="N45">
-        <v>6.2017169</v>
+        <v>6.1352452</v>
       </c>
       <c r="O45">
-        <v>2.170600915</v>
+        <v>2.14733582</v>
       </c>
       <c r="P45">
-        <v>4.031115985</v>
+        <v>3.98790938</v>
       </c>
       <c r="Q45">
-        <v>-5.028884015000001</v>
+        <v>-5.072090620000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2405799147125642</v>
+        <v>0.243241289987162</v>
       </c>
       <c r="T45">
-        <v>1.191249711258629</v>
+        <v>1.207526351137509</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.169735006305009</v>
+        <v>3.097695574343531</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5010,22 +5010,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1545477223928107</v>
+        <v>0.1540489433994598</v>
       </c>
       <c r="C46">
-        <v>78.99959959275992</v>
+        <v>78.53684657121983</v>
       </c>
       <c r="D46">
-        <v>124.6275995927599</v>
+        <v>125.2018465712198</v>
       </c>
       <c r="E46">
-        <v>45.628</v>
+        <v>46.665</v>
       </c>
       <c r="F46">
-        <v>45.628</v>
+        <v>46.665</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5046,28 +5046,28 @@
         <v>9.06</v>
       </c>
       <c r="M46">
-        <v>2.9247548</v>
+        <v>2.9912265</v>
       </c>
       <c r="N46">
-        <v>6.1352452</v>
+        <v>6.068773500000001</v>
       </c>
       <c r="O46">
-        <v>2.14733582</v>
+        <v>2.124070725</v>
       </c>
       <c r="P46">
-        <v>3.98790938</v>
+        <v>3.944702775000001</v>
       </c>
       <c r="Q46">
-        <v>-5.072090620000001</v>
+        <v>-5.115297225</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.243241289987162</v>
+        <v>0.2459994425444724</v>
       </c>
       <c r="T46">
-        <v>1.207526351137509</v>
+        <v>1.224394868830167</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.097695574343531</v>
+        <v>3.028857894913675</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5092,22 +5092,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1540489433994598</v>
+        <v>0.155882364406109</v>
       </c>
       <c r="C47">
-        <v>78.53684657121983</v>
+        <v>75.41461069521603</v>
       </c>
       <c r="D47">
-        <v>125.2018465712198</v>
+        <v>123.116610695216</v>
       </c>
       <c r="E47">
-        <v>46.665</v>
+        <v>47.70200000000001</v>
       </c>
       <c r="F47">
-        <v>46.665</v>
+        <v>47.70200000000001</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5128,45 +5128,45 @@
         <v>9.06</v>
       </c>
       <c r="M47">
-        <v>2.9912265</v>
+        <v>3.4297738</v>
       </c>
       <c r="N47">
-        <v>6.068773500000001</v>
+        <v>5.6302262</v>
       </c>
       <c r="O47">
-        <v>2.124070725</v>
+        <v>1.97057917</v>
       </c>
       <c r="P47">
-        <v>3.944702775000001</v>
+        <v>3.65964703</v>
       </c>
       <c r="Q47">
-        <v>-5.115297225</v>
+        <v>-5.40035297</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2459994425444724</v>
+        <v>0.2488597489002018</v>
       </c>
       <c r="T47">
-        <v>1.224394868830167</v>
+        <v>1.241888146437368</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.35</v>
       </c>
       <c r="W47">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.028857894913675</v>
+        <v>2.641573622143827</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5174,22 +5174,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.155882364406109</v>
+        <v>0.1554342854127581</v>
       </c>
       <c r="C48">
-        <v>75.41461069521603</v>
+        <v>74.88079240317718</v>
       </c>
       <c r="D48">
-        <v>123.116610695216</v>
+        <v>123.6197924031772</v>
       </c>
       <c r="E48">
-        <v>47.70200000000001</v>
+        <v>48.739</v>
       </c>
       <c r="F48">
-        <v>47.70200000000001</v>
+        <v>48.739</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5210,28 +5210,28 @@
         <v>9.06</v>
       </c>
       <c r="M48">
-        <v>3.4297738</v>
+        <v>3.504334100000001</v>
       </c>
       <c r="N48">
-        <v>5.6302262</v>
+        <v>5.555665899999999</v>
       </c>
       <c r="O48">
-        <v>1.97057917</v>
+        <v>1.944483065</v>
       </c>
       <c r="P48">
-        <v>3.65964703</v>
+        <v>3.611182835</v>
       </c>
       <c r="Q48">
-        <v>-5.40035297</v>
+        <v>-5.448817165000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2488597489002018</v>
+        <v>0.2518279913448265</v>
       </c>
       <c r="T48">
-        <v>1.241888146437368</v>
+        <v>1.26004154772786</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.641573622143827</v>
+        <v>2.585369928055661</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5256,22 +5256,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1554342854127581</v>
+        <v>0.1549862064194072</v>
       </c>
       <c r="C49">
-        <v>74.88079240317718</v>
+        <v>74.3511040312182</v>
       </c>
       <c r="D49">
-        <v>123.6197924031772</v>
+        <v>124.1271040312182</v>
       </c>
       <c r="E49">
-        <v>48.739</v>
+        <v>49.776</v>
       </c>
       <c r="F49">
-        <v>48.739</v>
+        <v>49.776</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5292,28 +5292,28 @@
         <v>9.06</v>
       </c>
       <c r="M49">
-        <v>3.504334100000001</v>
+        <v>3.578894400000001</v>
       </c>
       <c r="N49">
-        <v>5.555665899999999</v>
+        <v>5.481105599999999</v>
       </c>
       <c r="O49">
-        <v>1.944483065</v>
+        <v>1.91838696</v>
       </c>
       <c r="P49">
-        <v>3.611182835</v>
+        <v>3.56271864</v>
       </c>
       <c r="Q49">
-        <v>-5.448817165000001</v>
+        <v>-5.497281360000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2518279913448265</v>
+        <v>0.2549103969603985</v>
       </c>
       <c r="T49">
-        <v>1.26004154772786</v>
+        <v>1.278893156760293</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.585369928055661</v>
+        <v>2.531508054554501</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5338,22 +5338,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1549862064194072</v>
+        <v>0.1557802774260564</v>
       </c>
       <c r="C50">
-        <v>74.35110403121821</v>
+        <v>72.41789121236278</v>
       </c>
       <c r="D50">
-        <v>124.1271040312182</v>
+        <v>123.2308912123628</v>
       </c>
       <c r="E50">
-        <v>49.776</v>
+        <v>50.813</v>
       </c>
       <c r="F50">
-        <v>49.776</v>
+        <v>50.813</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5374,45 +5374,45 @@
         <v>9.06</v>
       </c>
       <c r="M50">
-        <v>3.5788944</v>
+        <v>3.851625400000001</v>
       </c>
       <c r="N50">
-        <v>5.481105600000001</v>
+        <v>5.2083746</v>
       </c>
       <c r="O50">
-        <v>1.91838696</v>
+        <v>1.82293111</v>
       </c>
       <c r="P50">
-        <v>3.562718640000001</v>
+        <v>3.38544349</v>
       </c>
       <c r="Q50">
-        <v>-5.49728136</v>
+        <v>-5.67455651</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2549103969603985</v>
+        <v>0.2581136812275615</v>
       </c>
       <c r="T50">
-        <v>1.278893156760293</v>
+        <v>1.298484044578313</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.35</v>
       </c>
       <c r="W50">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.531508054554502</v>
+        <v>2.352253674513622</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5420,22 +5420,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1557802774260564</v>
+        <v>0.1553575484327055</v>
       </c>
       <c r="C51">
-        <v>72.41789121236278</v>
+        <v>71.85637894768689</v>
       </c>
       <c r="D51">
-        <v>123.2308912123628</v>
+        <v>123.7063789476869</v>
       </c>
       <c r="E51">
-        <v>50.813</v>
+        <v>51.85</v>
       </c>
       <c r="F51">
-        <v>50.813</v>
+        <v>51.85</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5456,28 +5456,28 @@
         <v>9.06</v>
       </c>
       <c r="M51">
-        <v>3.851625400000001</v>
+        <v>3.93023</v>
       </c>
       <c r="N51">
-        <v>5.2083746</v>
+        <v>5.129770000000001</v>
       </c>
       <c r="O51">
-        <v>1.82293111</v>
+        <v>1.7954195</v>
       </c>
       <c r="P51">
-        <v>3.38544349</v>
+        <v>3.3343505</v>
       </c>
       <c r="Q51">
-        <v>-5.67455651</v>
+        <v>-5.7256495</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2581136812275615</v>
+        <v>0.261445096865411</v>
       </c>
       <c r="T51">
-        <v>1.298484044578313</v>
+        <v>1.318858567909053</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.352253674513622</v>
+        <v>2.30520860102335</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5502,22 +5502,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1553575484327055</v>
+        <v>0.1549348194393546</v>
       </c>
       <c r="C52">
-        <v>71.85637894768689</v>
+        <v>71.29855024528273</v>
       </c>
       <c r="D52">
-        <v>123.7063789476869</v>
+        <v>124.1855502452827</v>
       </c>
       <c r="E52">
-        <v>51.85</v>
+        <v>52.887</v>
       </c>
       <c r="F52">
-        <v>51.85</v>
+        <v>52.887</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5538,28 +5538,28 @@
         <v>9.06</v>
       </c>
       <c r="M52">
-        <v>3.93023</v>
+        <v>4.0088346</v>
       </c>
       <c r="N52">
-        <v>5.129770000000001</v>
+        <v>5.0511654</v>
       </c>
       <c r="O52">
-        <v>1.7954195</v>
+        <v>1.76790789</v>
       </c>
       <c r="P52">
-        <v>3.3343505</v>
+        <v>3.28325751</v>
       </c>
       <c r="Q52">
-        <v>-5.7256495</v>
+        <v>-5.77674249</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.261445096865411</v>
+        <v>0.264912488651744</v>
       </c>
       <c r="T52">
-        <v>1.318858567909053</v>
+        <v>1.340064704436966</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.30520860102335</v>
+        <v>2.260008432375833</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5584,22 +5584,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1549348194393546</v>
+        <v>0.1545120904460038</v>
       </c>
       <c r="C53">
-        <v>71.29855024528273</v>
+        <v>70.74444807595208</v>
       </c>
       <c r="D53">
-        <v>124.1855502452827</v>
+        <v>124.6684480759521</v>
       </c>
       <c r="E53">
-        <v>52.887</v>
+        <v>53.92400000000001</v>
       </c>
       <c r="F53">
-        <v>52.887</v>
+        <v>53.92400000000001</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5620,28 +5620,28 @@
         <v>9.06</v>
       </c>
       <c r="M53">
-        <v>4.0088346</v>
+        <v>4.087439200000001</v>
       </c>
       <c r="N53">
-        <v>5.0511654</v>
+        <v>4.972560799999999</v>
       </c>
       <c r="O53">
-        <v>1.76790789</v>
+        <v>1.74039628</v>
       </c>
       <c r="P53">
-        <v>3.28325751</v>
+        <v>3.23216452</v>
       </c>
       <c r="Q53">
-        <v>-5.77674249</v>
+        <v>-5.827835480000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.264912488651744</v>
+        <v>0.2685243550958411</v>
       </c>
       <c r="T53">
-        <v>1.340064704436966</v>
+        <v>1.362154429986875</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.260008432375833</v>
+        <v>2.21654673175322</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5666,22 +5666,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1545120904460038</v>
+        <v>0.1540893614526529</v>
       </c>
       <c r="C54">
-        <v>70.74444807595208</v>
+        <v>70.19411608147732</v>
       </c>
       <c r="D54">
-        <v>124.6684480759521</v>
+        <v>125.1551160814773</v>
       </c>
       <c r="E54">
-        <v>53.92400000000001</v>
+        <v>54.96100000000001</v>
       </c>
       <c r="F54">
-        <v>53.92400000000001</v>
+        <v>54.96100000000001</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5702,28 +5702,28 @@
         <v>9.06</v>
       </c>
       <c r="M54">
-        <v>4.087439200000001</v>
+        <v>4.166043800000001</v>
       </c>
       <c r="N54">
-        <v>4.972560799999999</v>
+        <v>4.8939562</v>
       </c>
       <c r="O54">
-        <v>1.74039628</v>
+        <v>1.71288467</v>
       </c>
       <c r="P54">
-        <v>3.23216452</v>
+        <v>3.18107153</v>
       </c>
       <c r="Q54">
-        <v>-5.827835480000001</v>
+        <v>-5.87892847</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2685243550958411</v>
+        <v>0.2722899179843678</v>
       </c>
       <c r="T54">
-        <v>1.362154429986875</v>
+        <v>1.385184143858057</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.21654673175322</v>
+        <v>2.174725095305047</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5748,22 +5748,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1540893614526529</v>
+        <v>0.153666632459302</v>
       </c>
       <c r="C55">
-        <v>70.19411608147732</v>
+        <v>69.64759858776858</v>
       </c>
       <c r="D55">
-        <v>125.1551160814773</v>
+        <v>125.6455985877686</v>
       </c>
       <c r="E55">
-        <v>54.96100000000001</v>
+        <v>55.998</v>
       </c>
       <c r="F55">
-        <v>54.96100000000001</v>
+        <v>55.998</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5784,28 +5784,28 @@
         <v>9.06</v>
       </c>
       <c r="M55">
-        <v>4.166043800000001</v>
+        <v>4.244648400000001</v>
       </c>
       <c r="N55">
-        <v>4.8939562</v>
+        <v>4.8153516</v>
       </c>
       <c r="O55">
-        <v>1.71288467</v>
+        <v>1.68537306</v>
       </c>
       <c r="P55">
-        <v>3.18107153</v>
+        <v>3.12997854</v>
       </c>
       <c r="Q55">
-        <v>-5.87892847</v>
+        <v>-5.930021460000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2722899179843678</v>
+        <v>0.2762192009984826</v>
       </c>
       <c r="T55">
-        <v>1.385184143858057</v>
+        <v>1.409215149636682</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.174725095305047</v>
+        <v>2.134452408354953</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5830,22 +5830,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.153666632459302</v>
+        <v>0.1532439034659511</v>
       </c>
       <c r="C56">
-        <v>69.64759858776858</v>
+        <v>69.1049406183223</v>
       </c>
       <c r="D56">
-        <v>125.6455985877686</v>
+        <v>126.1399406183223</v>
       </c>
       <c r="E56">
-        <v>55.998</v>
+        <v>57.035</v>
       </c>
       <c r="F56">
-        <v>55.998</v>
+        <v>57.035</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5866,28 +5866,28 @@
         <v>9.06</v>
       </c>
       <c r="M56">
-        <v>4.244648400000001</v>
+        <v>4.323253</v>
       </c>
       <c r="N56">
-        <v>4.8153516</v>
+        <v>4.736747</v>
       </c>
       <c r="O56">
-        <v>1.68537306</v>
+        <v>1.65786145</v>
       </c>
       <c r="P56">
-        <v>3.12997854</v>
+        <v>3.07888555</v>
       </c>
       <c r="Q56">
-        <v>-5.930021460000001</v>
+        <v>-5.98111445</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2762192009984826</v>
+        <v>0.2803231188132247</v>
       </c>
       <c r="T56">
-        <v>1.409215149636682</v>
+        <v>1.434314200116579</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.134452408354953</v>
+        <v>2.0956441827485</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5912,22 +5912,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1532439034659511</v>
+        <v>0.1528211744726002</v>
       </c>
       <c r="C57">
-        <v>69.1049406183223</v>
+        <v>68.56618790799834</v>
       </c>
       <c r="D57">
-        <v>126.1399406183223</v>
+        <v>126.6381879079984</v>
       </c>
       <c r="E57">
-        <v>57.035</v>
+        <v>58.07200000000001</v>
       </c>
       <c r="F57">
-        <v>57.035</v>
+        <v>58.07200000000001</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5948,28 +5948,28 @@
         <v>9.06</v>
       </c>
       <c r="M57">
-        <v>4.323253</v>
+        <v>4.401857600000001</v>
       </c>
       <c r="N57">
-        <v>4.736747</v>
+        <v>4.658142399999999</v>
       </c>
       <c r="O57">
-        <v>1.65786145</v>
+        <v>1.63034984</v>
       </c>
       <c r="P57">
-        <v>3.07888555</v>
+        <v>3.02779256</v>
       </c>
       <c r="Q57">
-        <v>-5.98111445</v>
+        <v>-6.032207440000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2803231188132247</v>
+        <v>0.2846135783468187</v>
       </c>
       <c r="T57">
-        <v>1.434314200116579</v>
+        <v>1.460554116527381</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.0956441827485</v>
+        <v>2.058221965199419</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5994,22 +5994,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1528211744726002</v>
+        <v>0.1523984454792494</v>
       </c>
       <c r="C58">
-        <v>68.56618790799834</v>
+        <v>68.03138691712506</v>
       </c>
       <c r="D58">
-        <v>126.6381879079984</v>
+        <v>127.1403869171251</v>
       </c>
       <c r="E58">
-        <v>58.07200000000001</v>
+        <v>59.10900000000001</v>
       </c>
       <c r="F58">
-        <v>58.07200000000001</v>
+        <v>59.10900000000001</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6030,28 +6030,28 @@
         <v>9.06</v>
       </c>
       <c r="M58">
-        <v>4.401857600000001</v>
+        <v>4.480462200000001</v>
       </c>
       <c r="N58">
-        <v>4.658142399999999</v>
+        <v>4.5795378</v>
       </c>
       <c r="O58">
-        <v>1.63034984</v>
+        <v>1.60283823</v>
       </c>
       <c r="P58">
-        <v>3.02779256</v>
+        <v>2.97669957</v>
       </c>
       <c r="Q58">
-        <v>-6.032207440000001</v>
+        <v>-6.08330043</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2846135783468187</v>
+        <v>0.2891035941377892</v>
       </c>
       <c r="T58">
-        <v>1.460554116527381</v>
+        <v>1.488014494166591</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6068,7 +6068,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.058221965199419</v>
+        <v>2.022112807915219</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6076,22 +6076,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1523984454792494</v>
+        <v>0.1573291164858985</v>
       </c>
       <c r="C59">
-        <v>68.03138691712506</v>
+        <v>61.3735460165726</v>
       </c>
       <c r="D59">
-        <v>127.1403869171251</v>
+        <v>121.5195460165726</v>
       </c>
       <c r="E59">
-        <v>59.10900000000001</v>
+        <v>60.14600000000001</v>
       </c>
       <c r="F59">
-        <v>59.10900000000001</v>
+        <v>60.14600000000001</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6112,45 +6112,45 @@
         <v>9.06</v>
       </c>
       <c r="M59">
-        <v>4.480462200000001</v>
+        <v>5.41314</v>
       </c>
       <c r="N59">
-        <v>4.5795378</v>
+        <v>3.64686</v>
       </c>
       <c r="O59">
-        <v>1.60283823</v>
+        <v>1.276401</v>
       </c>
       <c r="P59">
-        <v>2.97669957</v>
+        <v>2.370459</v>
       </c>
       <c r="Q59">
-        <v>-6.08330043</v>
+        <v>-6.689541</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2891035941377892</v>
+        <v>0.2938074202045202</v>
       </c>
       <c r="T59">
-        <v>1.488014494166591</v>
+        <v>1.516782508836241</v>
       </c>
       <c r="U59">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V59">
         <v>0.35</v>
       </c>
       <c r="W59">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.022112807915219</v>
+        <v>1.673705095379022</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6158,22 +6158,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1573291164858985</v>
+        <v>0.1569986874925476</v>
       </c>
       <c r="C60">
-        <v>61.37354601657258</v>
+        <v>60.69764363533184</v>
       </c>
       <c r="D60">
-        <v>121.5195460165726</v>
+        <v>121.8806436353318</v>
       </c>
       <c r="E60">
-        <v>60.146</v>
+        <v>61.183</v>
       </c>
       <c r="F60">
-        <v>60.146</v>
+        <v>61.183</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6194,28 +6194,28 @@
         <v>9.06</v>
       </c>
       <c r="M60">
-        <v>5.41314</v>
+        <v>5.50647</v>
       </c>
       <c r="N60">
-        <v>3.64686</v>
+        <v>3.55353</v>
       </c>
       <c r="O60">
-        <v>1.276401</v>
+        <v>1.2437355</v>
       </c>
       <c r="P60">
-        <v>2.370459</v>
+        <v>2.3097945</v>
       </c>
       <c r="Q60">
-        <v>-6.689541</v>
+        <v>-6.7502055</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2938074202045202</v>
+        <v>0.2987407012013356</v>
       </c>
       <c r="T60">
-        <v>1.516782508836241</v>
+        <v>1.546953841294653</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6232,7 +6232,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.673705095379022</v>
+        <v>1.645337212406496</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6240,22 +6240,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1569986874925476</v>
+        <v>0.1566682584991967</v>
       </c>
       <c r="C61">
-        <v>60.69764363533184</v>
+        <v>60.02389366677046</v>
       </c>
       <c r="D61">
-        <v>121.8806436353318</v>
+        <v>122.2438936667705</v>
       </c>
       <c r="E61">
-        <v>61.183</v>
+        <v>62.22</v>
       </c>
       <c r="F61">
-        <v>61.183</v>
+        <v>62.22</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6276,28 +6276,28 @@
         <v>9.06</v>
       </c>
       <c r="M61">
-        <v>5.50647</v>
+        <v>5.5998</v>
       </c>
       <c r="N61">
-        <v>3.55353</v>
+        <v>3.4602</v>
       </c>
       <c r="O61">
-        <v>1.2437355</v>
+        <v>1.21107</v>
       </c>
       <c r="P61">
-        <v>2.3097945</v>
+        <v>2.24913</v>
       </c>
       <c r="Q61">
-        <v>-6.7502055</v>
+        <v>-6.81087</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2987407012013356</v>
+        <v>0.3039206462479919</v>
       </c>
       <c r="T61">
-        <v>1.546953841294653</v>
+        <v>1.578633740375987</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.645337212406496</v>
+        <v>1.617914925533055</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6322,22 +6322,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1566682584991967</v>
+        <v>0.1563378295058459</v>
       </c>
       <c r="C62">
-        <v>60.02389366677046</v>
+        <v>59.35231541340848</v>
       </c>
       <c r="D62">
-        <v>122.2438936667705</v>
+        <v>122.6093154134085</v>
       </c>
       <c r="E62">
-        <v>62.22</v>
+        <v>63.257</v>
       </c>
       <c r="F62">
-        <v>62.22</v>
+        <v>63.257</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6358,28 +6358,28 @@
         <v>9.06</v>
       </c>
       <c r="M62">
-        <v>5.5998</v>
+        <v>5.69313</v>
       </c>
       <c r="N62">
-        <v>3.4602</v>
+        <v>3.36687</v>
       </c>
       <c r="O62">
-        <v>1.21107</v>
+        <v>1.1784045</v>
       </c>
       <c r="P62">
-        <v>2.24913</v>
+        <v>2.1884655</v>
       </c>
       <c r="Q62">
-        <v>-6.81087</v>
+        <v>-6.8715345</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3039206462479919</v>
+        <v>0.3093662295021689</v>
       </c>
       <c r="T62">
-        <v>1.578633740375987</v>
+        <v>1.61193824966662</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.617914925533055</v>
+        <v>1.591391730032513</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6404,22 +6404,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1563378295058459</v>
+        <v>0.156007400512495</v>
       </c>
       <c r="C63">
-        <v>59.35231541340848</v>
+        <v>58.68292840926077</v>
       </c>
       <c r="D63">
-        <v>122.6093154134085</v>
+        <v>122.9769284092608</v>
       </c>
       <c r="E63">
-        <v>63.257</v>
+        <v>64.294</v>
       </c>
       <c r="F63">
-        <v>63.257</v>
+        <v>64.294</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6440,28 +6440,28 @@
         <v>9.06</v>
       </c>
       <c r="M63">
-        <v>5.69313</v>
+        <v>5.78646</v>
       </c>
       <c r="N63">
-        <v>3.36687</v>
+        <v>3.273540000000001</v>
       </c>
       <c r="O63">
-        <v>1.1784045</v>
+        <v>1.145739</v>
       </c>
       <c r="P63">
-        <v>2.1884655</v>
+        <v>2.127801000000001</v>
       </c>
       <c r="Q63">
-        <v>-6.8715345</v>
+        <v>-6.932199</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3093662295021689</v>
+        <v>0.3150984224013027</v>
       </c>
       <c r="T63">
-        <v>1.61193824966662</v>
+        <v>1.646995627867286</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.591391730032513</v>
+        <v>1.565724121483602</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6486,22 +6486,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.156007400512495</v>
+        <v>0.1556769715191441</v>
       </c>
       <c r="C64">
-        <v>58.68292840926077</v>
+        <v>58.01575242331795</v>
       </c>
       <c r="D64">
-        <v>122.9769284092608</v>
+        <v>123.346752423318</v>
       </c>
       <c r="E64">
-        <v>64.294</v>
+        <v>65.331</v>
       </c>
       <c r="F64">
-        <v>64.294</v>
+        <v>65.331</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6522,28 +6522,28 @@
         <v>9.06</v>
       </c>
       <c r="M64">
-        <v>5.78646</v>
+        <v>5.87979</v>
       </c>
       <c r="N64">
-        <v>3.273540000000001</v>
+        <v>3.180210000000001</v>
       </c>
       <c r="O64">
-        <v>1.145739</v>
+        <v>1.1130735</v>
       </c>
       <c r="P64">
-        <v>2.127801000000001</v>
+        <v>2.067136500000001</v>
       </c>
       <c r="Q64">
-        <v>-6.932199</v>
+        <v>-6.9928635</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3150984224013027</v>
+        <v>0.3211404635652544</v>
       </c>
       <c r="T64">
-        <v>1.646995627867286</v>
+        <v>1.683947999484204</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.565724121483602</v>
+        <v>1.540871357650528</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6568,22 +6568,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1556769715191441</v>
+        <v>0.1553465425257933</v>
       </c>
       <c r="C65">
-        <v>58.01575242331795</v>
+        <v>57.35080746309005</v>
       </c>
       <c r="D65">
-        <v>123.346752423318</v>
+        <v>123.7188074630901</v>
       </c>
       <c r="E65">
-        <v>65.331</v>
+        <v>66.36800000000001</v>
       </c>
       <c r="F65">
-        <v>65.331</v>
+        <v>66.36800000000001</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6604,28 +6604,28 @@
         <v>9.06</v>
       </c>
       <c r="M65">
-        <v>5.87979</v>
+        <v>5.973120000000001</v>
       </c>
       <c r="N65">
-        <v>3.180210000000001</v>
+        <v>3.08688</v>
       </c>
       <c r="O65">
-        <v>1.1130735</v>
+        <v>1.080408</v>
       </c>
       <c r="P65">
-        <v>2.067136500000001</v>
+        <v>2.006472</v>
       </c>
       <c r="Q65">
-        <v>-6.9928635</v>
+        <v>-7.053528</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3211404635652544</v>
+        <v>0.3275181736827591</v>
       </c>
       <c r="T65">
-        <v>1.683947999484204</v>
+        <v>1.722953280635396</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.540871357650528</v>
+        <v>1.516795242687239</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6650,22 +6650,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1553465425257933</v>
+        <v>0.1843417107974887</v>
       </c>
       <c r="C66">
-        <v>57.35080746309005</v>
+        <v>30.42090040920368</v>
       </c>
       <c r="D66">
-        <v>123.7188074630901</v>
+        <v>97.82590040920368</v>
       </c>
       <c r="E66">
-        <v>66.36800000000001</v>
+        <v>67.405</v>
       </c>
       <c r="F66">
-        <v>66.36800000000001</v>
+        <v>67.405</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6686,45 +6686,45 @@
         <v>9.06</v>
       </c>
       <c r="M66">
-        <v>5.973120000000001</v>
+        <v>9.895054000000002</v>
       </c>
       <c r="N66">
-        <v>3.08688</v>
+        <v>-0.8350540000000013</v>
       </c>
       <c r="O66">
-        <v>1.080408</v>
+        <v>-0.2922689000000004</v>
       </c>
       <c r="P66">
-        <v>2.006472</v>
+        <v>-0.5427851000000008</v>
       </c>
       <c r="Q66">
-        <v>-7.053528</v>
+        <v>-9.602785100000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3275181736827591</v>
+        <v>0.3414294368287526</v>
       </c>
       <c r="T66">
-        <v>1.722953280635396</v>
+        <v>1.808032834296575</v>
       </c>
       <c r="U66">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.35</v>
+        <v>0.3204631323891713</v>
       </c>
       <c r="W66">
-        <v>0.0585</v>
+        <v>0.09975601216526965</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.516795242687239</v>
+        <v>0.9156089496833467</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6732,22 +6732,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1843417107974887</v>
+        <v>0.1853517107974887</v>
       </c>
       <c r="C67">
-        <v>30.42090040920368</v>
+        <v>28.6758893153327</v>
       </c>
       <c r="D67">
-        <v>97.82590040920368</v>
+        <v>97.1178893153327</v>
       </c>
       <c r="E67">
-        <v>67.405</v>
+        <v>68.44200000000001</v>
       </c>
       <c r="F67">
-        <v>67.405</v>
+        <v>68.44200000000001</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6768,37 +6768,37 @@
         <v>9.06</v>
       </c>
       <c r="M67">
-        <v>9.895054000000002</v>
+        <v>10.0472856</v>
       </c>
       <c r="N67">
-        <v>-0.8350540000000013</v>
+        <v>-0.9872856000000017</v>
       </c>
       <c r="O67">
-        <v>-0.2922689000000004</v>
+        <v>-0.3455499600000005</v>
       </c>
       <c r="P67">
-        <v>-0.5427851000000008</v>
+        <v>-0.6417356400000012</v>
       </c>
       <c r="Q67">
-        <v>-9.602785100000002</v>
+        <v>-9.701735640000003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3414294368287526</v>
+        <v>0.3501244202648924</v>
       </c>
       <c r="T67">
-        <v>1.808032834296575</v>
+        <v>1.861210270599415</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.3204631323891713</v>
+        <v>0.3156076303832748</v>
       </c>
       <c r="W67">
-        <v>0.09975601216526965</v>
+        <v>0.1004687998597353</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9156089496833467</v>
+        <v>0.9017360868093566</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6814,22 +6814,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1853517107974887</v>
+        <v>0.1863617107974886</v>
       </c>
       <c r="C68">
-        <v>28.6758893153327</v>
+        <v>26.94105298670547</v>
       </c>
       <c r="D68">
-        <v>97.1178893153327</v>
+        <v>96.42005298670547</v>
       </c>
       <c r="E68">
-        <v>68.44200000000001</v>
+        <v>69.479</v>
       </c>
       <c r="F68">
-        <v>68.44200000000001</v>
+        <v>69.479</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6850,37 +6850,37 @@
         <v>9.06</v>
       </c>
       <c r="M68">
-        <v>10.0472856</v>
+        <v>10.1995172</v>
       </c>
       <c r="N68">
-        <v>-0.9872856000000017</v>
+        <v>-1.1395172</v>
       </c>
       <c r="O68">
-        <v>-0.3455499600000005</v>
+        <v>-0.39883102</v>
       </c>
       <c r="P68">
-        <v>-0.6417356400000012</v>
+        <v>-0.7406861800000002</v>
       </c>
       <c r="Q68">
-        <v>-9.701735640000003</v>
+        <v>-9.800686180000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3501244202648924</v>
+        <v>0.3593463723941315</v>
       </c>
       <c r="T68">
-        <v>1.861210270599415</v>
+        <v>1.917610581829701</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.3156076303832748</v>
+        <v>0.3108970687357633</v>
       </c>
       <c r="W68">
-        <v>0.1004687998597353</v>
+        <v>0.10116031030959</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9017360868093566</v>
+        <v>0.8882773392450379</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6896,22 +6896,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1863617107974886</v>
+        <v>0.1873717107974887</v>
       </c>
       <c r="C69">
-        <v>26.94105298670547</v>
+        <v>25.21617365708519</v>
       </c>
       <c r="D69">
-        <v>96.42005298670547</v>
+        <v>95.7321736570852</v>
       </c>
       <c r="E69">
-        <v>69.479</v>
+        <v>70.51600000000001</v>
       </c>
       <c r="F69">
-        <v>69.479</v>
+        <v>70.51600000000001</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6932,37 +6932,37 @@
         <v>9.06</v>
       </c>
       <c r="M69">
-        <v>10.1995172</v>
+        <v>10.3517488</v>
       </c>
       <c r="N69">
-        <v>-1.1395172</v>
+        <v>-1.291748800000001</v>
       </c>
       <c r="O69">
-        <v>-0.39883102</v>
+        <v>-0.4521120800000002</v>
       </c>
       <c r="P69">
-        <v>-0.7406861800000002</v>
+        <v>-0.8396367200000003</v>
       </c>
       <c r="Q69">
-        <v>-9.800686180000001</v>
+        <v>-9.89963672</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3593463723941315</v>
+        <v>0.3691446965314482</v>
       </c>
       <c r="T69">
-        <v>1.917610581829701</v>
+        <v>1.977535912511879</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.3108970687357633</v>
+        <v>0.3063250530190609</v>
       </c>
       <c r="W69">
-        <v>0.10116031030959</v>
+        <v>0.1018314822168019</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8882773392450379</v>
+        <v>0.8752144371973168</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6978,22 +6978,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1873717107974887</v>
+        <v>0.1883817107974887</v>
       </c>
       <c r="C70">
-        <v>25.21617365708519</v>
+        <v>23.50103973056085</v>
       </c>
       <c r="D70">
-        <v>95.7321736570852</v>
+        <v>95.05403973056086</v>
       </c>
       <c r="E70">
-        <v>70.51600000000001</v>
+        <v>71.55300000000001</v>
       </c>
       <c r="F70">
-        <v>70.51600000000001</v>
+        <v>71.55300000000001</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7014,37 +7014,37 @@
         <v>9.06</v>
       </c>
       <c r="M70">
-        <v>10.3517488</v>
+        <v>10.5039804</v>
       </c>
       <c r="N70">
-        <v>-1.291748800000001</v>
+        <v>-1.443980400000003</v>
       </c>
       <c r="O70">
-        <v>-0.4521120800000002</v>
+        <v>-0.5053931400000009</v>
       </c>
       <c r="P70">
-        <v>-0.8396367200000003</v>
+        <v>-0.9385872600000018</v>
       </c>
       <c r="Q70">
-        <v>-9.89963672</v>
+        <v>-9.998587260000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3691446965314482</v>
+        <v>0.3795751706131078</v>
       </c>
       <c r="T70">
-        <v>1.977535912511879</v>
+        <v>2.041327393560649</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.3063250530190609</v>
+        <v>0.3018855594970454</v>
       </c>
       <c r="W70">
-        <v>0.1018314822168019</v>
+        <v>0.1024831998658337</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8752144371973168</v>
+        <v>0.8625301699915584</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7060,22 +7060,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1883817107974887</v>
+        <v>0.1893917107974887</v>
       </c>
       <c r="C71">
-        <v>23.50103973056085</v>
+        <v>21.79544556454201</v>
       </c>
       <c r="D71">
-        <v>95.05403973056086</v>
+        <v>94.38544556454201</v>
       </c>
       <c r="E71">
-        <v>71.55300000000001</v>
+        <v>72.59</v>
       </c>
       <c r="F71">
-        <v>71.55300000000001</v>
+        <v>72.59</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7096,37 +7096,37 @@
         <v>9.06</v>
       </c>
       <c r="M71">
-        <v>10.5039804</v>
+        <v>10.656212</v>
       </c>
       <c r="N71">
-        <v>-1.443980400000003</v>
+        <v>-1.596212000000001</v>
       </c>
       <c r="O71">
-        <v>-0.5053931400000009</v>
+        <v>-0.5586742000000005</v>
       </c>
       <c r="P71">
-        <v>-0.9385872600000018</v>
+        <v>-1.037537800000001</v>
       </c>
       <c r="Q71">
-        <v>-9.998587260000003</v>
+        <v>-10.0975378</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3795751706131078</v>
+        <v>0.3907010096335448</v>
       </c>
       <c r="T71">
-        <v>2.041327393560649</v>
+        <v>2.109371640012671</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.3018855594970454</v>
+        <v>0.2975729086470877</v>
       </c>
       <c r="W71">
-        <v>0.1024831998658337</v>
+        <v>0.1031162970106075</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8625301699915584</v>
+        <v>0.8502083104202506</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7142,22 +7142,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1893917107974887</v>
+        <v>0.1904017107974887</v>
       </c>
       <c r="C72">
-        <v>21.79544556454201</v>
+        <v>20.09919126184779</v>
       </c>
       <c r="D72">
-        <v>94.38544556454201</v>
+        <v>93.7261912618478</v>
       </c>
       <c r="E72">
-        <v>72.59</v>
+        <v>73.62700000000001</v>
       </c>
       <c r="F72">
-        <v>72.59</v>
+        <v>73.62700000000001</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7178,37 +7178,37 @@
         <v>9.06</v>
       </c>
       <c r="M72">
-        <v>10.656212</v>
+        <v>10.8084436</v>
       </c>
       <c r="N72">
-        <v>-1.596212000000001</v>
+        <v>-1.748443600000002</v>
       </c>
       <c r="O72">
-        <v>-0.5586742000000005</v>
+        <v>-0.6119552600000006</v>
       </c>
       <c r="P72">
-        <v>-1.037537800000001</v>
+        <v>-1.136488340000001</v>
       </c>
       <c r="Q72">
-        <v>-10.0975378</v>
+        <v>-10.19648834</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3907010096335448</v>
+        <v>0.4025941478967704</v>
       </c>
       <c r="T72">
-        <v>2.109371640012671</v>
+        <v>2.182108593116556</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2975729086470877</v>
+        <v>0.2933817409196639</v>
       </c>
       <c r="W72">
-        <v>0.1031162970106075</v>
+        <v>0.1037315604329933</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8502083104202506</v>
+        <v>0.838233545484754</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7224,22 +7224,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1904017107974887</v>
+        <v>0.1914117107974887</v>
       </c>
       <c r="C73">
-        <v>20.09919126184781</v>
+        <v>18.41208247144891</v>
       </c>
       <c r="D73">
-        <v>93.7261912618478</v>
+        <v>93.07608247144891</v>
       </c>
       <c r="E73">
-        <v>73.627</v>
+        <v>74.664</v>
       </c>
       <c r="F73">
-        <v>73.627</v>
+        <v>74.664</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7260,37 +7260,37 @@
         <v>9.06</v>
       </c>
       <c r="M73">
-        <v>10.8084436</v>
+        <v>10.9606752</v>
       </c>
       <c r="N73">
-        <v>-1.7484436</v>
+        <v>-1.9006752</v>
       </c>
       <c r="O73">
-        <v>-0.6119552599999999</v>
+        <v>-0.66523632</v>
       </c>
       <c r="P73">
-        <v>-1.13648834</v>
+        <v>-1.23543888</v>
       </c>
       <c r="Q73">
-        <v>-10.19648834</v>
+        <v>-10.29543888</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4025941478967704</v>
+        <v>0.4153367960359407</v>
       </c>
       <c r="T73">
-        <v>2.182108593116556</v>
+        <v>2.260041042870718</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.293381740919664</v>
+        <v>0.2893069945180019</v>
       </c>
       <c r="W73">
-        <v>0.1037315604329933</v>
+        <v>0.1043297332047573</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8382335454847542</v>
+        <v>0.826591412908577</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7306,22 +7306,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1914117107974887</v>
+        <v>0.1924217107974887</v>
       </c>
       <c r="C74">
-        <v>18.41208247144891</v>
+        <v>16.73393019744496</v>
       </c>
       <c r="D74">
-        <v>93.07608247144891</v>
+        <v>92.43493019744496</v>
       </c>
       <c r="E74">
-        <v>74.664</v>
+        <v>75.70099999999999</v>
       </c>
       <c r="F74">
-        <v>74.664</v>
+        <v>75.70099999999999</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7342,37 +7342,37 @@
         <v>9.06</v>
       </c>
       <c r="M74">
-        <v>10.9606752</v>
+        <v>11.1129068</v>
       </c>
       <c r="N74">
-        <v>-1.9006752</v>
+        <v>-2.052906799999999</v>
       </c>
       <c r="O74">
-        <v>-0.66523632</v>
+        <v>-0.7185173799999995</v>
       </c>
       <c r="P74">
-        <v>-1.23543888</v>
+        <v>-1.334389419999999</v>
       </c>
       <c r="Q74">
-        <v>-10.29543888</v>
+        <v>-10.39438942</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4153367960359407</v>
+        <v>0.4290233440372718</v>
       </c>
       <c r="T74">
-        <v>2.260041042870718</v>
+        <v>2.343746266680745</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2893069945180019</v>
+        <v>0.2853438850040567</v>
       </c>
       <c r="W74">
-        <v>0.1043297332047573</v>
+        <v>0.1049115176814045</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.826591412908577</v>
+        <v>0.8152682428687336</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7388,22 +7388,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1924217107974887</v>
+        <v>0.1934317107974887</v>
       </c>
       <c r="C75">
-        <v>16.73393019744496</v>
+        <v>15.06455061588279</v>
       </c>
       <c r="D75">
-        <v>92.43493019744496</v>
+        <v>91.80255061588279</v>
       </c>
       <c r="E75">
-        <v>75.70099999999999</v>
+        <v>76.738</v>
       </c>
       <c r="F75">
-        <v>75.70099999999999</v>
+        <v>76.738</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7424,37 +7424,37 @@
         <v>9.06</v>
       </c>
       <c r="M75">
-        <v>11.1129068</v>
+        <v>11.2651384</v>
       </c>
       <c r="N75">
-        <v>-2.052906799999999</v>
+        <v>-2.205138400000001</v>
       </c>
       <c r="O75">
-        <v>-0.7185173799999995</v>
+        <v>-0.7717984400000003</v>
       </c>
       <c r="P75">
-        <v>-1.334389419999999</v>
+        <v>-1.433339960000001</v>
       </c>
       <c r="Q75">
-        <v>-10.39438942</v>
+        <v>-10.49333996</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4290233440372718</v>
+        <v>0.4437627034233208</v>
       </c>
       <c r="T75">
-        <v>2.343746266680745</v>
+        <v>2.433890353860774</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2853438850040567</v>
+        <v>0.281487886558056</v>
       </c>
       <c r="W75">
-        <v>0.1049115176814045</v>
+        <v>0.1054775782532774</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8152682428687336</v>
+        <v>0.8042511044515884</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7470,22 +7470,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1934317107974887</v>
+        <v>0.2422628240512239</v>
       </c>
       <c r="C76">
-        <v>15.06455061588279</v>
+        <v>-8.790103399602188</v>
       </c>
       <c r="D76">
-        <v>91.80255061588279</v>
+        <v>68.98489660039782</v>
       </c>
       <c r="E76">
-        <v>76.738</v>
+        <v>77.77500000000001</v>
       </c>
       <c r="F76">
-        <v>76.738</v>
+        <v>77.77500000000001</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7506,45 +7506,45 @@
         <v>9.06</v>
       </c>
       <c r="M76">
-        <v>11.2651384</v>
+        <v>15.61722</v>
       </c>
       <c r="N76">
-        <v>-2.205138400000001</v>
+        <v>-6.557220000000001</v>
       </c>
       <c r="O76">
-        <v>-0.7717984400000003</v>
+        <v>-2.295027</v>
       </c>
       <c r="P76">
-        <v>-1.433339960000001</v>
+        <v>-4.262193000000001</v>
       </c>
       <c r="Q76">
-        <v>-10.49333996</v>
+        <v>-13.322193</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4437627034233208</v>
+        <v>0.4889656645751944</v>
       </c>
       <c r="T76">
-        <v>2.433890353860774</v>
+        <v>2.710346037187608</v>
       </c>
       <c r="U76">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.281487886558056</v>
+        <v>0.2030451002162997</v>
       </c>
       <c r="W76">
-        <v>0.1054775782532774</v>
+        <v>0.160028543876567</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.8042511044515884</v>
+        <v>0.5801288577608563</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7552,22 +7552,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2422628240512239</v>
+        <v>0.2438128240512238</v>
       </c>
       <c r="C77">
-        <v>-8.790103399602188</v>
+        <v>-10.36710170649444</v>
       </c>
       <c r="D77">
-        <v>68.98489660039782</v>
+        <v>68.44489829350556</v>
       </c>
       <c r="E77">
-        <v>77.77500000000001</v>
+        <v>78.812</v>
       </c>
       <c r="F77">
-        <v>77.77500000000001</v>
+        <v>78.812</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7588,37 +7588,37 @@
         <v>9.06</v>
       </c>
       <c r="M77">
-        <v>15.61722</v>
+        <v>15.8254496</v>
       </c>
       <c r="N77">
-        <v>-6.557220000000001</v>
+        <v>-6.7654496</v>
       </c>
       <c r="O77">
-        <v>-2.295027</v>
+        <v>-2.36790736</v>
       </c>
       <c r="P77">
-        <v>-4.262193000000001</v>
+        <v>-4.39754224</v>
       </c>
       <c r="Q77">
-        <v>-13.322193</v>
+        <v>-13.45754224</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4889656645751944</v>
+        <v>0.5074309005991607</v>
       </c>
       <c r="T77">
-        <v>2.710346037187608</v>
+        <v>2.823277122070425</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.2030451002162997</v>
+        <v>0.2003734541608221</v>
       </c>
       <c r="W77">
-        <v>0.160028543876567</v>
+        <v>0.1605650104045069</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5801288577608563</v>
+        <v>0.5724955833166345</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7634,22 +7634,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2438128240512238</v>
+        <v>0.2453628240512238</v>
       </c>
       <c r="C78">
-        <v>-10.36710170649444</v>
+        <v>-11.93571170379386</v>
       </c>
       <c r="D78">
-        <v>68.44489829350556</v>
+        <v>67.91328829620615</v>
       </c>
       <c r="E78">
-        <v>78.812</v>
+        <v>79.849</v>
       </c>
       <c r="F78">
-        <v>78.812</v>
+        <v>79.849</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7670,37 +7670,37 @@
         <v>9.06</v>
       </c>
       <c r="M78">
-        <v>15.8254496</v>
+        <v>16.0336792</v>
       </c>
       <c r="N78">
-        <v>-6.7654496</v>
+        <v>-6.973679200000001</v>
       </c>
       <c r="O78">
-        <v>-2.36790736</v>
+        <v>-2.44078772</v>
       </c>
       <c r="P78">
-        <v>-4.39754224</v>
+        <v>-4.532891480000001</v>
       </c>
       <c r="Q78">
-        <v>-13.45754224</v>
+        <v>-13.59289148</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5074309005991607</v>
+        <v>0.5275018093208634</v>
       </c>
       <c r="T78">
-        <v>2.823277122070425</v>
+        <v>2.946028301290878</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.2003734541608221</v>
+        <v>0.1977712015093828</v>
       </c>
       <c r="W78">
-        <v>0.1605650104045069</v>
+        <v>0.1610875427369159</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5724955833166345</v>
+        <v>0.5650605757410938</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7716,22 +7716,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2453628240512238</v>
+        <v>0.2469128240512238</v>
       </c>
       <c r="C79">
-        <v>-11.93571170379386</v>
+        <v>-13.49612734054266</v>
       </c>
       <c r="D79">
-        <v>67.91328829620615</v>
+        <v>67.38987265945735</v>
       </c>
       <c r="E79">
-        <v>79.849</v>
+        <v>80.88600000000001</v>
       </c>
       <c r="F79">
-        <v>79.849</v>
+        <v>80.88600000000001</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7752,37 +7752,37 @@
         <v>9.06</v>
       </c>
       <c r="M79">
-        <v>16.0336792</v>
+        <v>16.2419088</v>
       </c>
       <c r="N79">
-        <v>-6.973679200000001</v>
+        <v>-7.1819088</v>
       </c>
       <c r="O79">
-        <v>-2.44078772</v>
+        <v>-2.51366808</v>
       </c>
       <c r="P79">
-        <v>-4.532891480000001</v>
+        <v>-4.66824072</v>
       </c>
       <c r="Q79">
-        <v>-13.59289148</v>
+        <v>-13.72824072</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5275018093208634</v>
+        <v>0.5493973461081754</v>
       </c>
       <c r="T79">
-        <v>2.946028301290878</v>
+        <v>3.079938678622282</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1977712015093828</v>
+        <v>0.1952356732849035</v>
       </c>
       <c r="W79">
-        <v>0.1610875427369159</v>
+        <v>0.1615966768043914</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5650605757410938</v>
+        <v>0.5578162093854387</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7798,22 +7798,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2469128240512238</v>
+        <v>0.2484628240512239</v>
       </c>
       <c r="C80">
-        <v>-13.49612734054266</v>
+        <v>-15.04853663236106</v>
       </c>
       <c r="D80">
-        <v>67.38987265945735</v>
+        <v>66.87446336763894</v>
       </c>
       <c r="E80">
-        <v>80.88600000000001</v>
+        <v>81.923</v>
       </c>
       <c r="F80">
-        <v>80.88600000000001</v>
+        <v>81.923</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7834,37 +7834,37 @@
         <v>9.06</v>
       </c>
       <c r="M80">
-        <v>16.2419088</v>
+        <v>16.4501384</v>
       </c>
       <c r="N80">
-        <v>-7.1819088</v>
+        <v>-7.3901384</v>
       </c>
       <c r="O80">
-        <v>-2.51366808</v>
+        <v>-2.58654844</v>
       </c>
       <c r="P80">
-        <v>-4.66824072</v>
+        <v>-4.80358996</v>
       </c>
       <c r="Q80">
-        <v>-13.72824072</v>
+        <v>-13.86358996</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5493973461081754</v>
+        <v>0.5733781721133266</v>
       </c>
       <c r="T80">
-        <v>3.079938678622282</v>
+        <v>3.226602425223343</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1952356732849035</v>
+        <v>0.1927643356483858</v>
       </c>
       <c r="W80">
-        <v>0.1615966768043914</v>
+        <v>0.1620929214018041</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5578162093854387</v>
+        <v>0.5507552447096737</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7880,22 +7880,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2484628240512239</v>
+        <v>0.2500128240512238</v>
       </c>
       <c r="C81">
-        <v>-15.04853663236106</v>
+        <v>-16.59312188662423</v>
       </c>
       <c r="D81">
-        <v>66.87446336763894</v>
+        <v>66.36687811337578</v>
       </c>
       <c r="E81">
-        <v>81.923</v>
+        <v>82.96000000000001</v>
       </c>
       <c r="F81">
-        <v>81.923</v>
+        <v>82.96000000000001</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7916,37 +7916,37 @@
         <v>9.06</v>
       </c>
       <c r="M81">
-        <v>16.4501384</v>
+        <v>16.658368</v>
       </c>
       <c r="N81">
-        <v>-7.3901384</v>
+        <v>-7.598368000000002</v>
       </c>
       <c r="O81">
-        <v>-2.58654844</v>
+        <v>-2.659428800000001</v>
       </c>
       <c r="P81">
-        <v>-4.80358996</v>
+        <v>-4.938939200000002</v>
       </c>
       <c r="Q81">
-        <v>-13.86358996</v>
+        <v>-13.9989392</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5733781721133266</v>
+        <v>0.5997570807189929</v>
       </c>
       <c r="T81">
-        <v>3.226602425223343</v>
+        <v>3.38793254648451</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1927643356483858</v>
+        <v>0.1903547814527809</v>
       </c>
       <c r="W81">
-        <v>0.1620929214018041</v>
+        <v>0.1625767598842816</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5507552447096737</v>
+        <v>0.5438708041508027</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7962,22 +7962,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2500128240512238</v>
+        <v>0.2515628240512239</v>
       </c>
       <c r="C82">
-        <v>-16.59312188662423</v>
+        <v>-18.13005991746175</v>
       </c>
       <c r="D82">
-        <v>66.36687811337578</v>
+        <v>65.86694008253826</v>
       </c>
       <c r="E82">
-        <v>82.96000000000001</v>
+        <v>83.99700000000001</v>
       </c>
       <c r="F82">
-        <v>82.96000000000001</v>
+        <v>83.99700000000001</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7998,37 +7998,37 @@
         <v>9.06</v>
       </c>
       <c r="M82">
-        <v>16.658368</v>
+        <v>16.8665976</v>
       </c>
       <c r="N82">
-        <v>-7.598368000000002</v>
+        <v>-7.806597600000002</v>
       </c>
       <c r="O82">
-        <v>-2.659428800000001</v>
+        <v>-2.73230916</v>
       </c>
       <c r="P82">
-        <v>-4.938939200000002</v>
+        <v>-5.074288440000002</v>
       </c>
       <c r="Q82">
-        <v>-13.9989392</v>
+        <v>-14.13428844</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5997570807189929</v>
+        <v>0.6289127165463085</v>
       </c>
       <c r="T82">
-        <v>3.38793254648451</v>
+        <v>3.566244785773169</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1903547814527809</v>
+        <v>0.1880047224224997</v>
       </c>
       <c r="W82">
-        <v>0.1625767598842816</v>
+        <v>0.1630486517375621</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5438708041508027</v>
+        <v>0.5371563497785705</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8044,22 +8044,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2515628240512239</v>
+        <v>0.2531128240512238</v>
       </c>
       <c r="C83">
-        <v>-18.13005991746175</v>
+        <v>-19.65952225111219</v>
       </c>
       <c r="D83">
-        <v>65.86694008253826</v>
+        <v>65.37447774888781</v>
       </c>
       <c r="E83">
-        <v>83.99700000000001</v>
+        <v>85.03400000000001</v>
       </c>
       <c r="F83">
-        <v>83.99700000000001</v>
+        <v>85.03400000000001</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8080,37 +8080,37 @@
         <v>9.06</v>
       </c>
       <c r="M83">
-        <v>16.8665976</v>
+        <v>17.0748272</v>
       </c>
       <c r="N83">
-        <v>-7.806597600000002</v>
+        <v>-8.014827200000001</v>
       </c>
       <c r="O83">
-        <v>-2.73230916</v>
+        <v>-2.80518952</v>
       </c>
       <c r="P83">
-        <v>-5.074288440000002</v>
+        <v>-5.20963768</v>
       </c>
       <c r="Q83">
-        <v>-14.13428844</v>
+        <v>-14.26963768</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6289127165463085</v>
+        <v>0.6613078674655478</v>
       </c>
       <c r="T83">
-        <v>3.566244785773169</v>
+        <v>3.764369496093901</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1880047224224997</v>
+        <v>0.1857119819051521</v>
       </c>
       <c r="W83">
-        <v>0.1630486517375621</v>
+        <v>0.1635090340334455</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5371563497785705</v>
+        <v>0.5306056625861491</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8126,22 +8126,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2531128240512238</v>
+        <v>0.2546628240512239</v>
       </c>
       <c r="C84">
-        <v>-19.65952225111219</v>
+        <v>-21.18167532213421</v>
       </c>
       <c r="D84">
-        <v>65.37447774888781</v>
+        <v>64.8893246778658</v>
       </c>
       <c r="E84">
-        <v>85.03400000000001</v>
+        <v>86.07100000000001</v>
       </c>
       <c r="F84">
-        <v>85.03400000000001</v>
+        <v>86.07100000000001</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8162,37 +8162,37 @@
         <v>9.06</v>
       </c>
       <c r="M84">
-        <v>17.0748272</v>
+        <v>17.2830568</v>
       </c>
       <c r="N84">
-        <v>-8.014827200000001</v>
+        <v>-8.223056800000004</v>
       </c>
       <c r="O84">
-        <v>-2.80518952</v>
+        <v>-2.878069880000001</v>
       </c>
       <c r="P84">
-        <v>-5.20963768</v>
+        <v>-5.344986920000002</v>
       </c>
       <c r="Q84">
-        <v>-14.26963768</v>
+        <v>-14.40498692</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6613078674655478</v>
+        <v>0.6975142126105801</v>
       </c>
       <c r="T84">
-        <v>3.764369496093901</v>
+        <v>3.985802995864131</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1857119819051521</v>
+        <v>0.1834744881472587</v>
       </c>
       <c r="W84">
-        <v>0.1635090340334455</v>
+        <v>0.1639583227800304</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5306056625861491</v>
+        <v>0.5242128232778821</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8208,22 +8208,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2546628240512239</v>
+        <v>0.2562128240512239</v>
       </c>
       <c r="C85">
-        <v>-21.18167532213421</v>
+        <v>-22.69668066094475</v>
       </c>
       <c r="D85">
-        <v>64.8893246778658</v>
+        <v>64.41131933905525</v>
       </c>
       <c r="E85">
-        <v>86.07100000000001</v>
+        <v>87.108</v>
       </c>
       <c r="F85">
-        <v>86.07100000000001</v>
+        <v>87.108</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8244,37 +8244,37 @@
         <v>9.06</v>
       </c>
       <c r="M85">
-        <v>17.2830568</v>
+        <v>17.4912864</v>
       </c>
       <c r="N85">
-        <v>-8.223056800000004</v>
+        <v>-8.431286399999999</v>
       </c>
       <c r="O85">
-        <v>-2.878069880000001</v>
+        <v>-2.95095024</v>
       </c>
       <c r="P85">
-        <v>-5.344986920000002</v>
+        <v>-5.48033616</v>
       </c>
       <c r="Q85">
-        <v>-14.40498692</v>
+        <v>-14.54033616</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6975142126105801</v>
+        <v>0.7382463508987414</v>
       </c>
       <c r="T85">
-        <v>3.985802995864131</v>
+        <v>4.234915683105639</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1834744881472587</v>
+        <v>0.1812902680502676</v>
       </c>
       <c r="W85">
-        <v>0.1639583227800304</v>
+        <v>0.1643969141755063</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5242128232778821</v>
+        <v>0.5179721944293361</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8290,22 +8290,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2562128240512239</v>
+        <v>0.2577628240512239</v>
       </c>
       <c r="C86">
-        <v>-22.69668066094475</v>
+        <v>-24.20469507312963</v>
       </c>
       <c r="D86">
-        <v>64.41131933905525</v>
+        <v>63.94030492687036</v>
       </c>
       <c r="E86">
-        <v>87.108</v>
+        <v>88.145</v>
       </c>
       <c r="F86">
-        <v>87.108</v>
+        <v>88.145</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8326,37 +8326,37 @@
         <v>9.06</v>
       </c>
       <c r="M86">
-        <v>17.4912864</v>
+        <v>17.699516</v>
       </c>
       <c r="N86">
-        <v>-8.431286399999999</v>
+        <v>-8.639515999999999</v>
       </c>
       <c r="O86">
-        <v>-2.95095024</v>
+        <v>-3.023830599999999</v>
       </c>
       <c r="P86">
-        <v>-5.48033616</v>
+        <v>-5.615685399999999</v>
       </c>
       <c r="Q86">
-        <v>-14.54033616</v>
+        <v>-14.6756854</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7382463508987409</v>
+        <v>0.7844094409586571</v>
       </c>
       <c r="T86">
-        <v>4.234915683105636</v>
+        <v>4.517243395312679</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1812902680502676</v>
+        <v>0.1791574413673233</v>
       </c>
       <c r="W86">
-        <v>0.1643969141755063</v>
+        <v>0.1648251857734415</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5179721944293361</v>
+        <v>0.511878403906638</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8372,22 +8372,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2577628240512239</v>
+        <v>0.2593128240512239</v>
       </c>
       <c r="C87">
-        <v>-24.20469507312963</v>
+        <v>-25.70587081094327</v>
       </c>
       <c r="D87">
-        <v>63.94030492687036</v>
+        <v>63.47612918905673</v>
       </c>
       <c r="E87">
-        <v>88.145</v>
+        <v>89.182</v>
       </c>
       <c r="F87">
-        <v>88.145</v>
+        <v>89.182</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8408,37 +8408,37 @@
         <v>9.06</v>
       </c>
       <c r="M87">
-        <v>17.699516</v>
+        <v>17.9077456</v>
       </c>
       <c r="N87">
-        <v>-8.639515999999999</v>
+        <v>-8.847745600000001</v>
       </c>
       <c r="O87">
-        <v>-3.023830599999999</v>
+        <v>-3.09671096</v>
       </c>
       <c r="P87">
-        <v>-5.615685399999999</v>
+        <v>-5.751034640000001</v>
       </c>
       <c r="Q87">
-        <v>-14.6756854</v>
+        <v>-14.81103464</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7844094409586571</v>
+        <v>0.8371672581699897</v>
       </c>
       <c r="T87">
-        <v>4.517243395312679</v>
+        <v>4.839903637835013</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1791574413673233</v>
+        <v>0.1770742153049125</v>
       </c>
       <c r="W87">
-        <v>0.1648251857734415</v>
+        <v>0.1652434975667736</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.511878403906638</v>
+        <v>0.5059263294426072</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8454,22 +8454,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2593128240512239</v>
+        <v>0.2608628240512239</v>
       </c>
       <c r="C88">
-        <v>-25.70587081094327</v>
+        <v>-27.2003557373925</v>
       </c>
       <c r="D88">
-        <v>63.47612918905673</v>
+        <v>63.01864426260751</v>
       </c>
       <c r="E88">
-        <v>89.182</v>
+        <v>90.21900000000001</v>
       </c>
       <c r="F88">
-        <v>89.182</v>
+        <v>90.21900000000001</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8490,37 +8490,37 @@
         <v>9.06</v>
       </c>
       <c r="M88">
-        <v>17.9077456</v>
+        <v>18.1159752</v>
       </c>
       <c r="N88">
-        <v>-8.847745600000001</v>
+        <v>-9.055975200000001</v>
       </c>
       <c r="O88">
-        <v>-3.09671096</v>
+        <v>-3.16959132</v>
       </c>
       <c r="P88">
-        <v>-5.751034640000001</v>
+        <v>-5.88638388</v>
       </c>
       <c r="Q88">
-        <v>-14.81103464</v>
+        <v>-14.94638388</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8371672581699897</v>
+        <v>0.8980416626446044</v>
       </c>
       <c r="T88">
-        <v>4.839903637835013</v>
+        <v>5.212203917668476</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1770742153049125</v>
+        <v>0.1750388794968101</v>
       </c>
       <c r="W88">
-        <v>0.1652434975667736</v>
+        <v>0.1656521929970405</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5059263294426072</v>
+        <v>0.5001110842766002</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8536,22 +8536,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2608628240512239</v>
+        <v>0.2961669816783475</v>
       </c>
       <c r="C89">
-        <v>-27.2003557373925</v>
+        <v>-37.12359199578622</v>
       </c>
       <c r="D89">
-        <v>63.01864426260751</v>
+        <v>54.13240800421378</v>
       </c>
       <c r="E89">
-        <v>90.21900000000001</v>
+        <v>91.256</v>
       </c>
       <c r="F89">
-        <v>90.21900000000001</v>
+        <v>91.256</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8572,45 +8572,45 @@
         <v>9.06</v>
       </c>
       <c r="M89">
-        <v>18.1159752</v>
+        <v>21.5181648</v>
       </c>
       <c r="N89">
-        <v>-9.055975200000001</v>
+        <v>-12.4581648</v>
       </c>
       <c r="O89">
-        <v>-3.16959132</v>
+        <v>-4.36035768</v>
       </c>
       <c r="P89">
-        <v>-5.88638388</v>
+        <v>-8.097807120000001</v>
       </c>
       <c r="Q89">
-        <v>-14.94638388</v>
+        <v>-17.15780712</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8980416626446044</v>
+        <v>0.9936797814243522</v>
       </c>
       <c r="T89">
-        <v>5.212203917668476</v>
+        <v>5.797114746640844</v>
       </c>
       <c r="U89">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1750388794968101</v>
+        <v>0.1473638681306131</v>
       </c>
       <c r="W89">
-        <v>0.1656521929970405</v>
+        <v>0.2010515998948015</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.5001110842766002</v>
+        <v>0.4210396232303231</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8618,22 +8618,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2961669816783475</v>
+        <v>0.2980669816783476</v>
       </c>
       <c r="C90">
-        <v>-37.12359199578622</v>
+        <v>-38.56830121925942</v>
       </c>
       <c r="D90">
-        <v>54.13240800421378</v>
+        <v>53.72469878074059</v>
       </c>
       <c r="E90">
-        <v>91.256</v>
+        <v>92.29300000000001</v>
       </c>
       <c r="F90">
-        <v>91.256</v>
+        <v>92.29300000000001</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8654,37 +8654,37 @@
         <v>9.06</v>
       </c>
       <c r="M90">
-        <v>21.5181648</v>
+        <v>21.7626894</v>
       </c>
       <c r="N90">
-        <v>-12.4581648</v>
+        <v>-12.7026894</v>
       </c>
       <c r="O90">
-        <v>-4.36035768</v>
+        <v>-4.44594129</v>
       </c>
       <c r="P90">
-        <v>-8.097807120000001</v>
+        <v>-8.256748110000002</v>
       </c>
       <c r="Q90">
-        <v>-17.15780712</v>
+        <v>-17.31674811</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9936797814243522</v>
+        <v>1.079850670644748</v>
       </c>
       <c r="T90">
-        <v>5.797114746640844</v>
+        <v>6.324125178153649</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1473638681306131</v>
+        <v>0.1457080943313927</v>
       </c>
       <c r="W90">
-        <v>0.2010515998948015</v>
+        <v>0.2014420313566576</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4210396232303231</v>
+        <v>0.4163088409468363</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8700,22 +8700,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2980669816783476</v>
+        <v>0.2999669816783475</v>
       </c>
       <c r="C91">
-        <v>-38.56830121925942</v>
+        <v>-40.0069148632086</v>
       </c>
       <c r="D91">
-        <v>53.72469878074059</v>
+        <v>53.3230851367914</v>
       </c>
       <c r="E91">
-        <v>92.29300000000001</v>
+        <v>93.33</v>
       </c>
       <c r="F91">
-        <v>92.29300000000001</v>
+        <v>93.33</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8736,37 +8736,37 @@
         <v>9.06</v>
       </c>
       <c r="M91">
-        <v>21.7626894</v>
+        <v>22.007214</v>
       </c>
       <c r="N91">
-        <v>-12.7026894</v>
+        <v>-12.947214</v>
       </c>
       <c r="O91">
-        <v>-4.44594129</v>
+        <v>-4.5315249</v>
       </c>
       <c r="P91">
-        <v>-8.256748110000002</v>
+        <v>-8.415689100000002</v>
       </c>
       <c r="Q91">
-        <v>-17.31674811</v>
+        <v>-17.4756891</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.079850670644748</v>
+        <v>1.183255737709223</v>
       </c>
       <c r="T91">
-        <v>6.324125178153649</v>
+        <v>6.956537695969013</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1457080943313927</v>
+        <v>0.1440891155054883</v>
       </c>
       <c r="W91">
-        <v>0.2014420313566576</v>
+        <v>0.2018237865638059</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4163088409468363</v>
+        <v>0.4116831871585381</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8782,22 +8782,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2999669816783475</v>
+        <v>0.3018669816783476</v>
       </c>
       <c r="C92">
-        <v>-40.0069148632086</v>
+        <v>-41.43956861401966</v>
       </c>
       <c r="D92">
-        <v>53.3230851367914</v>
+        <v>52.92743138598034</v>
       </c>
       <c r="E92">
-        <v>93.33</v>
+        <v>94.367</v>
       </c>
       <c r="F92">
-        <v>93.33</v>
+        <v>94.367</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8818,37 +8818,37 @@
         <v>9.06</v>
       </c>
       <c r="M92">
-        <v>22.007214</v>
+        <v>22.2517386</v>
       </c>
       <c r="N92">
-        <v>-12.947214</v>
+        <v>-13.1917386</v>
       </c>
       <c r="O92">
-        <v>-4.5315249</v>
+        <v>-4.61710851</v>
       </c>
       <c r="P92">
-        <v>-8.415689100000002</v>
+        <v>-8.574630090000003</v>
       </c>
       <c r="Q92">
-        <v>-17.4756891</v>
+        <v>-17.63463009</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.183255737709223</v>
+        <v>1.309639708565804</v>
       </c>
       <c r="T92">
-        <v>6.956537695969013</v>
+        <v>7.729486328854462</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1440891155054883</v>
+        <v>0.1425057186318016</v>
       </c>
       <c r="W92">
-        <v>0.2018237865638059</v>
+        <v>0.2021971515466212</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4116831871585381</v>
+        <v>0.4071591960908618</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8864,22 +8864,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3018669816783476</v>
+        <v>0.3037669816783476</v>
       </c>
       <c r="C93">
-        <v>-41.43956861401966</v>
+        <v>-42.86639416060359</v>
       </c>
       <c r="D93">
-        <v>52.92743138598034</v>
+        <v>52.53760583939642</v>
       </c>
       <c r="E93">
-        <v>94.367</v>
+        <v>95.40400000000001</v>
       </c>
       <c r="F93">
-        <v>94.367</v>
+        <v>95.40400000000001</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8900,37 +8900,37 @@
         <v>9.06</v>
       </c>
       <c r="M93">
-        <v>22.2517386</v>
+        <v>22.4962632</v>
       </c>
       <c r="N93">
-        <v>-13.1917386</v>
+        <v>-13.4362632</v>
       </c>
       <c r="O93">
-        <v>-4.61710851</v>
+        <v>-4.702692120000001</v>
       </c>
       <c r="P93">
-        <v>-8.574630090000003</v>
+        <v>-8.733571080000004</v>
       </c>
       <c r="Q93">
-        <v>-17.63463009</v>
+        <v>-17.79357108000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.309639708565804</v>
+        <v>1.467619672136529</v>
       </c>
       <c r="T93">
-        <v>7.729486328854462</v>
+        <v>8.695672119961271</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1425057186318016</v>
+        <v>0.140956743429282</v>
       </c>
       <c r="W93">
-        <v>0.2021971515466212</v>
+        <v>0.2025623998993753</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4071591960908618</v>
+        <v>0.4027335526550916</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8946,22 +8946,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3037669816783476</v>
+        <v>0.3056669816783476</v>
       </c>
       <c r="C94">
-        <v>-42.86639416060359</v>
+        <v>-44.28751934053277</v>
       </c>
       <c r="D94">
-        <v>52.53760583939642</v>
+        <v>52.15348065946723</v>
       </c>
       <c r="E94">
-        <v>95.40400000000001</v>
+        <v>96.441</v>
       </c>
       <c r="F94">
-        <v>95.40400000000001</v>
+        <v>96.441</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8982,37 +8982,37 @@
         <v>9.06</v>
       </c>
       <c r="M94">
-        <v>22.4962632</v>
+        <v>22.7407878</v>
       </c>
       <c r="N94">
-        <v>-13.4362632</v>
+        <v>-13.6807878</v>
       </c>
       <c r="O94">
-        <v>-4.702692120000001</v>
+        <v>-4.788275730000001</v>
       </c>
       <c r="P94">
-        <v>-8.733571080000004</v>
+        <v>-8.892512070000002</v>
       </c>
       <c r="Q94">
-        <v>-17.79357108000001</v>
+        <v>-17.95251207</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.467619672136529</v>
+        <v>1.670736768156034</v>
       </c>
       <c r="T94">
-        <v>8.695672119961271</v>
+        <v>9.937910994241454</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.140956743429282</v>
+        <v>0.1394410795214403</v>
       </c>
       <c r="W94">
-        <v>0.2025623998993753</v>
+        <v>0.2029197934488444</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4027335526550916</v>
+        <v>0.3984030843469724</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9028,22 +9028,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3056669816783476</v>
+        <v>0.3075669816783476</v>
       </c>
       <c r="C95">
-        <v>-44.28751934053277</v>
+        <v>-45.70306827981325</v>
       </c>
       <c r="D95">
-        <v>52.15348065946723</v>
+        <v>51.77493172018676</v>
       </c>
       <c r="E95">
-        <v>96.441</v>
+        <v>97.47800000000001</v>
       </c>
       <c r="F95">
-        <v>96.441</v>
+        <v>97.47800000000001</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9064,37 +9064,37 @@
         <v>9.06</v>
       </c>
       <c r="M95">
-        <v>22.7407878</v>
+        <v>22.9853124</v>
       </c>
       <c r="N95">
-        <v>-13.6807878</v>
+        <v>-13.9253124</v>
       </c>
       <c r="O95">
-        <v>-4.788275730000001</v>
+        <v>-4.87385934</v>
       </c>
       <c r="P95">
-        <v>-8.892512070000002</v>
+        <v>-9.05145306</v>
       </c>
       <c r="Q95">
-        <v>-17.95251207</v>
+        <v>-18.11145306</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.670736768156034</v>
+        <v>1.941559562848707</v>
       </c>
       <c r="T95">
-        <v>9.937910994241454</v>
+        <v>11.5942294932817</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1394410795214403</v>
+        <v>0.1379576637818505</v>
       </c>
       <c r="W95">
-        <v>0.2029197934488444</v>
+        <v>0.2032695828802397</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3984030843469724</v>
+        <v>0.3941647536624301</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9110,22 +9110,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3075669816783476</v>
+        <v>0.3094669816783476</v>
       </c>
       <c r="C96">
-        <v>-45.70306827981325</v>
+        <v>-47.11316152661333</v>
       </c>
       <c r="D96">
-        <v>51.77493172018676</v>
+        <v>51.40183847338668</v>
       </c>
       <c r="E96">
-        <v>97.47800000000001</v>
+        <v>98.51500000000001</v>
       </c>
       <c r="F96">
-        <v>97.47800000000001</v>
+        <v>98.51500000000001</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9146,37 +9146,37 @@
         <v>9.06</v>
       </c>
       <c r="M96">
-        <v>22.9853124</v>
+        <v>23.229837</v>
       </c>
       <c r="N96">
-        <v>-13.9253124</v>
+        <v>-14.169837</v>
       </c>
       <c r="O96">
-        <v>-4.87385934</v>
+        <v>-4.959442950000001</v>
       </c>
       <c r="P96">
-        <v>-9.05145306</v>
+        <v>-9.210394050000001</v>
       </c>
       <c r="Q96">
-        <v>-18.11145306</v>
+        <v>-18.27039405</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.941559562848707</v>
+        <v>2.320711475418449</v>
       </c>
       <c r="T96">
-        <v>11.5942294932817</v>
+        <v>13.91307539193805</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1379576637818505</v>
+        <v>0.1365054778473047</v>
       </c>
       <c r="W96">
-        <v>0.2032695828802397</v>
+        <v>0.2036120083236056</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3941647536624301</v>
+        <v>0.3900156509922992</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9192,22 +9192,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3094669816783476</v>
+        <v>0.3113669816783476</v>
       </c>
       <c r="C97">
-        <v>-47.11316152661333</v>
+        <v>-48.51791617925206</v>
       </c>
       <c r="D97">
-        <v>51.40183847338668</v>
+        <v>51.03408382074795</v>
       </c>
       <c r="E97">
-        <v>98.51500000000001</v>
+        <v>99.55200000000001</v>
       </c>
       <c r="F97">
-        <v>98.51500000000001</v>
+        <v>99.55200000000001</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9228,37 +9228,37 @@
         <v>9.06</v>
       </c>
       <c r="M97">
-        <v>23.229837</v>
+        <v>23.4743616</v>
       </c>
       <c r="N97">
-        <v>-14.169837</v>
+        <v>-14.4143616</v>
       </c>
       <c r="O97">
-        <v>-4.959442950000001</v>
+        <v>-5.04502656</v>
       </c>
       <c r="P97">
-        <v>-9.210394050000001</v>
+        <v>-9.369335040000001</v>
       </c>
       <c r="Q97">
-        <v>-18.27039405</v>
+        <v>-18.42933504</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.320711475418449</v>
+        <v>2.889439344273062</v>
       </c>
       <c r="T97">
-        <v>13.91307539193805</v>
+        <v>17.39134423992257</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1365054778473047</v>
+        <v>0.1350835457863953</v>
       </c>
       <c r="W97">
-        <v>0.2036120083236056</v>
+        <v>0.203947299903568</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3900156509922992</v>
+        <v>0.3859529879611294</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9274,22 +9274,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3113669816783475</v>
+        <v>0.3132669816783475</v>
       </c>
       <c r="C98">
-        <v>-48.51791617925203</v>
+        <v>-49.91744600873218</v>
       </c>
       <c r="D98">
-        <v>51.03408382074796</v>
+        <v>50.67155399126781</v>
       </c>
       <c r="E98">
-        <v>99.55199999999999</v>
+        <v>100.589</v>
       </c>
       <c r="F98">
-        <v>99.55199999999999</v>
+        <v>100.589</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9310,37 +9310,37 @@
         <v>9.06</v>
       </c>
       <c r="M98">
-        <v>23.4743616</v>
+        <v>23.7188862</v>
       </c>
       <c r="N98">
-        <v>-14.4143616</v>
+        <v>-14.6588862</v>
       </c>
       <c r="O98">
-        <v>-5.045026559999999</v>
+        <v>-5.13061017</v>
       </c>
       <c r="P98">
-        <v>-9.369335039999999</v>
+        <v>-9.528276030000001</v>
       </c>
       <c r="Q98">
-        <v>-18.42933504</v>
+        <v>-18.58827603</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.889439344273054</v>
+        <v>3.837319125697407</v>
       </c>
       <c r="T98">
-        <v>17.39134423992252</v>
+        <v>23.18845898656336</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1350835457863953</v>
+        <v>0.1336909319123088</v>
       </c>
       <c r="W98">
-        <v>0.203947299903568</v>
+        <v>0.2042756782550776</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3859529879611295</v>
+        <v>0.3819740911780251</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9356,22 +9356,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3132669816783475</v>
+        <v>0.3151669816783476</v>
       </c>
       <c r="C99">
-        <v>-49.91744600873218</v>
+        <v>-51.31186157608771</v>
       </c>
       <c r="D99">
-        <v>50.67155399126781</v>
+        <v>50.3141384239123</v>
       </c>
       <c r="E99">
-        <v>100.589</v>
+        <v>101.626</v>
       </c>
       <c r="F99">
-        <v>100.589</v>
+        <v>101.626</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9392,37 +9392,37 @@
         <v>9.06</v>
       </c>
       <c r="M99">
-        <v>23.7188862</v>
+        <v>23.9634108</v>
       </c>
       <c r="N99">
-        <v>-14.6588862</v>
+        <v>-14.9034108</v>
       </c>
       <c r="O99">
-        <v>-5.13061017</v>
+        <v>-5.21619378</v>
       </c>
       <c r="P99">
-        <v>-9.528276030000001</v>
+        <v>-9.687217020000002</v>
       </c>
       <c r="Q99">
-        <v>-18.58827603</v>
+        <v>-18.74721702</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.837319125697407</v>
+        <v>5.733078688546109</v>
       </c>
       <c r="T99">
-        <v>23.18845898656336</v>
+        <v>34.78268847984504</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1336909319123088</v>
+        <v>0.1323267387295301</v>
       </c>
       <c r="W99">
-        <v>0.2042756782550776</v>
+        <v>0.2045973550075768</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3819740911780251</v>
+        <v>0.3780763963700861</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9438,22 +9438,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3151669816783476</v>
+        <v>0.3170669816783476</v>
       </c>
       <c r="C100">
-        <v>-51.31186157608771</v>
+        <v>-52.7012703447995</v>
       </c>
       <c r="D100">
-        <v>50.3141384239123</v>
+        <v>49.96172965520049</v>
       </c>
       <c r="E100">
-        <v>101.626</v>
+        <v>102.663</v>
       </c>
       <c r="F100">
-        <v>101.626</v>
+        <v>102.663</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9474,37 +9474,37 @@
         <v>9.06</v>
       </c>
       <c r="M100">
-        <v>23.9634108</v>
+        <v>24.2079354</v>
       </c>
       <c r="N100">
-        <v>-14.9034108</v>
+        <v>-15.1479354</v>
       </c>
       <c r="O100">
-        <v>-5.21619378</v>
+        <v>-5.30177739</v>
       </c>
       <c r="P100">
-        <v>-9.687217020000002</v>
+        <v>-9.84615801</v>
       </c>
       <c r="Q100">
-        <v>-18.74721702</v>
+        <v>-18.90615801</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.733078688546109</v>
+        <v>11.42035737709222</v>
       </c>
       <c r="T100">
-        <v>34.78268847984504</v>
+        <v>69.56537695969007</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1323267387295301</v>
+        <v>0.1309901050049894</v>
       </c>
       <c r="W100">
-        <v>0.2045973550075768</v>
+        <v>0.2049125332398235</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9512,91 +9512,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3780763963700861</v>
+        <v>0.3742574428713983</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3170669816783476</v>
-      </c>
-      <c r="C101">
-        <v>-52.7012703447995</v>
-      </c>
-      <c r="D101">
-        <v>49.96172965520049</v>
-      </c>
-      <c r="E101">
-        <v>102.663</v>
-      </c>
-      <c r="F101">
-        <v>102.663</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>103.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>-9.06</v>
-      </c>
-      <c r="L101">
-        <v>9.06</v>
-      </c>
-      <c r="M101">
-        <v>24.2079354</v>
-      </c>
-      <c r="N101">
-        <v>-15.1479354</v>
-      </c>
-      <c r="O101">
-        <v>-5.30177739</v>
-      </c>
-      <c r="P101">
-        <v>-9.84615801</v>
-      </c>
-      <c r="Q101">
-        <v>-18.90615801</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.42035737709222</v>
-      </c>
-      <c r="T101">
-        <v>69.56537695969007</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1309901050049894</v>
-      </c>
-      <c r="W101">
-        <v>0.2049125332398235</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3742574428713983</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
